--- a/data/dataframe/10085.xlsx
+++ b/data/dataframe/10085.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tug83224/Desktop/xsec_JAM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shujie/jlab/CJ/CJ-database/data/dataframe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B35949-60D0-814A-AED2-0AE81E97FF3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A252D451-ED53-B245-B30B-EB3C00E2A5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30720" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3060" yWindow="1600" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="format" sheetId="1" r:id="rId1"/>
@@ -85,9 +85,6 @@
     <t>JLab JLCEE96</t>
   </si>
   <si>
-    <t>col</t>
-  </si>
-  <si>
     <t>%*norm_c</t>
   </si>
   <si>
@@ -107,6 +104,9 @@
   </si>
   <si>
     <t>NC</t>
+  </si>
+  <si>
+    <t>exp</t>
   </si>
 </sst>
 </file>
@@ -528,10 +528,10 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B1" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -567,7 +567,7 @@
         <v>8</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>9</v>
@@ -591,13 +591,13 @@
         <v>18</v>
       </c>
       <c r="W1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y1" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.2">
@@ -671,10 +671,10 @@
         <v>1.26</v>
       </c>
       <c r="X2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.2">
@@ -748,10 +748,10 @@
         <v>1.26</v>
       </c>
       <c r="X3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.2">
@@ -825,10 +825,10 @@
         <v>1.26</v>
       </c>
       <c r="X4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
@@ -902,10 +902,10 @@
         <v>1.26</v>
       </c>
       <c r="X5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.2">
@@ -979,10 +979,10 @@
         <v>1.26</v>
       </c>
       <c r="X6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.2">
@@ -1056,10 +1056,10 @@
         <v>1.26</v>
       </c>
       <c r="X7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.2">
@@ -1133,10 +1133,10 @@
         <v>1.26</v>
       </c>
       <c r="X8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.2">
@@ -1210,10 +1210,10 @@
         <v>1.26</v>
       </c>
       <c r="X9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.2">
@@ -1287,10 +1287,10 @@
         <v>1.26</v>
       </c>
       <c r="X10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.2">
@@ -1364,10 +1364,10 @@
         <v>1.26</v>
       </c>
       <c r="X11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.2">
@@ -1441,10 +1441,10 @@
         <v>1.26</v>
       </c>
       <c r="X12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.2">
@@ -1518,10 +1518,10 @@
         <v>1.26</v>
       </c>
       <c r="X13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.2">
@@ -1595,10 +1595,10 @@
         <v>1.26</v>
       </c>
       <c r="X14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.2">
@@ -1672,10 +1672,10 @@
         <v>1.26</v>
       </c>
       <c r="X15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.2">
@@ -1749,10 +1749,10 @@
         <v>1.26</v>
       </c>
       <c r="X16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.2">
@@ -1826,10 +1826,10 @@
         <v>1.26</v>
       </c>
       <c r="X17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.2">
@@ -1903,10 +1903,10 @@
         <v>1.26</v>
       </c>
       <c r="X18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.2">
@@ -1980,10 +1980,10 @@
         <v>1.26</v>
       </c>
       <c r="X19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.2">
@@ -2057,10 +2057,10 @@
         <v>1.26</v>
       </c>
       <c r="X20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.2">
@@ -2134,10 +2134,10 @@
         <v>1.26</v>
       </c>
       <c r="X21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.2">
@@ -2211,10 +2211,10 @@
         <v>1.26</v>
       </c>
       <c r="X22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.2">
@@ -2288,10 +2288,10 @@
         <v>1.26</v>
       </c>
       <c r="X23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.2">
@@ -2365,10 +2365,10 @@
         <v>1.26</v>
       </c>
       <c r="X24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.2">
@@ -2442,10 +2442,10 @@
         <v>1.26</v>
       </c>
       <c r="X25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.2">
@@ -2519,10 +2519,10 @@
         <v>1.26</v>
       </c>
       <c r="X26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.2">
@@ -2596,10 +2596,10 @@
         <v>1.26</v>
       </c>
       <c r="X27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.2">
@@ -2673,10 +2673,10 @@
         <v>1.26</v>
       </c>
       <c r="X28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.2">
@@ -2750,10 +2750,10 @@
         <v>1.26</v>
       </c>
       <c r="X29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.2">
@@ -2827,10 +2827,10 @@
         <v>1.26</v>
       </c>
       <c r="X30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.2">
@@ -2904,10 +2904,10 @@
         <v>1.26</v>
       </c>
       <c r="X31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.2">
@@ -2981,10 +2981,10 @@
         <v>1.26</v>
       </c>
       <c r="X32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.2">
@@ -3058,10 +3058,10 @@
         <v>1.26</v>
       </c>
       <c r="X33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.2">
@@ -3135,10 +3135,10 @@
         <v>1.26</v>
       </c>
       <c r="X34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.2">
@@ -3212,10 +3212,10 @@
         <v>1.26</v>
       </c>
       <c r="X35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.2">
@@ -3289,10 +3289,10 @@
         <v>1.26</v>
       </c>
       <c r="X36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.2">
@@ -3366,10 +3366,10 @@
         <v>1.26</v>
       </c>
       <c r="X37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.2">
@@ -3443,10 +3443,10 @@
         <v>1.26</v>
       </c>
       <c r="X38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.2">
@@ -3520,10 +3520,10 @@
         <v>1.26</v>
       </c>
       <c r="X39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.2">
@@ -3597,10 +3597,10 @@
         <v>1.26</v>
       </c>
       <c r="X40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.2">
@@ -3674,10 +3674,10 @@
         <v>1.26</v>
       </c>
       <c r="X41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.2">
@@ -3751,10 +3751,10 @@
         <v>1.26</v>
       </c>
       <c r="X42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.2">
@@ -3828,10 +3828,10 @@
         <v>1.26</v>
       </c>
       <c r="X43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y43" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.2">
@@ -3905,10 +3905,10 @@
         <v>1.26</v>
       </c>
       <c r="X44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.2">
@@ -3982,10 +3982,10 @@
         <v>1.26</v>
       </c>
       <c r="X45" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.2">
@@ -4059,10 +4059,10 @@
         <v>1.26</v>
       </c>
       <c r="X46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.2">
@@ -4136,10 +4136,10 @@
         <v>1.26</v>
       </c>
       <c r="X47" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y47" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.2">
@@ -4213,10 +4213,10 @@
         <v>1.26</v>
       </c>
       <c r="X48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.2">
@@ -4290,10 +4290,10 @@
         <v>1.26</v>
       </c>
       <c r="X49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y49" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.2">
@@ -4367,10 +4367,10 @@
         <v>1.26</v>
       </c>
       <c r="X50" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y50" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.2">
@@ -4444,10 +4444,10 @@
         <v>1.26</v>
       </c>
       <c r="X51" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.2">
@@ -4521,10 +4521,10 @@
         <v>1.26</v>
       </c>
       <c r="X52" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.2">
@@ -4598,10 +4598,10 @@
         <v>1.26</v>
       </c>
       <c r="X53" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.2">
@@ -4675,10 +4675,10 @@
         <v>1.26</v>
       </c>
       <c r="X54" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.2">
@@ -4752,10 +4752,10 @@
         <v>1.26</v>
       </c>
       <c r="X55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y55" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.2">
@@ -4829,10 +4829,10 @@
         <v>1.26</v>
       </c>
       <c r="X56" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.2">
@@ -4906,10 +4906,10 @@
         <v>1.26</v>
       </c>
       <c r="X57" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.2">
@@ -4983,10 +4983,10 @@
         <v>1.26</v>
       </c>
       <c r="X58" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y58" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.2">
@@ -5060,10 +5060,10 @@
         <v>1.26</v>
       </c>
       <c r="X59" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.2">
@@ -5137,10 +5137,10 @@
         <v>1.26</v>
       </c>
       <c r="X60" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.2">
@@ -5214,10 +5214,10 @@
         <v>1.26</v>
       </c>
       <c r="X61" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y61" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.2">
@@ -5291,10 +5291,10 @@
         <v>1.26</v>
       </c>
       <c r="X62" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y62" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.2">
@@ -5368,10 +5368,10 @@
         <v>1.26</v>
       </c>
       <c r="X63" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y63" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.2">
@@ -5445,10 +5445,10 @@
         <v>1.26</v>
       </c>
       <c r="X64" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y64" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.2">
@@ -5522,10 +5522,10 @@
         <v>1.26</v>
       </c>
       <c r="X65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y65" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.2">
@@ -5599,10 +5599,10 @@
         <v>1.26</v>
       </c>
       <c r="X66" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y66" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.2">
@@ -5676,10 +5676,10 @@
         <v>1.26</v>
       </c>
       <c r="X67" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y67" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.2">
@@ -5753,10 +5753,10 @@
         <v>1.26</v>
       </c>
       <c r="X68" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y68" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.2">
@@ -5830,10 +5830,10 @@
         <v>1.26</v>
       </c>
       <c r="X69" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y69" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.2">
@@ -5907,10 +5907,10 @@
         <v>1.26</v>
       </c>
       <c r="X70" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y70" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.2">
@@ -5984,10 +5984,10 @@
         <v>1.26</v>
       </c>
       <c r="X71" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y71" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.2">
@@ -6061,10 +6061,10 @@
         <v>1.26</v>
       </c>
       <c r="X72" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.2">
@@ -6138,10 +6138,10 @@
         <v>1.26</v>
       </c>
       <c r="X73" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y73" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.2">
@@ -6215,10 +6215,10 @@
         <v>1.26</v>
       </c>
       <c r="X74" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y74" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.2">
@@ -6292,10 +6292,10 @@
         <v>1.26</v>
       </c>
       <c r="X75" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y75" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.2">
@@ -6369,10 +6369,10 @@
         <v>1.26</v>
       </c>
       <c r="X76" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.2">
@@ -6446,10 +6446,10 @@
         <v>1.26</v>
       </c>
       <c r="X77" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y77" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.2">
@@ -6523,10 +6523,10 @@
         <v>1.26</v>
       </c>
       <c r="X78" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y78" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.2">
@@ -6600,10 +6600,10 @@
         <v>1.26</v>
       </c>
       <c r="X79" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y79" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.2">
@@ -6677,10 +6677,10 @@
         <v>1.26</v>
       </c>
       <c r="X80" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y80" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.2">
@@ -6754,10 +6754,10 @@
         <v>1.26</v>
       </c>
       <c r="X81" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y81" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.2">
@@ -6831,10 +6831,10 @@
         <v>1.26</v>
       </c>
       <c r="X82" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y82" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.2">
@@ -6908,10 +6908,10 @@
         <v>1.26</v>
       </c>
       <c r="X83" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y83" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.2">
@@ -6985,10 +6985,10 @@
         <v>1.26</v>
       </c>
       <c r="X84" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y84" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.2">
@@ -7062,10 +7062,10 @@
         <v>1.26</v>
       </c>
       <c r="X85" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y85" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.2">
@@ -7139,10 +7139,10 @@
         <v>1.26</v>
       </c>
       <c r="X86" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y86" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.2">
@@ -7216,10 +7216,10 @@
         <v>1.26</v>
       </c>
       <c r="X87" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y87" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.2">
@@ -7293,10 +7293,10 @@
         <v>1.26</v>
       </c>
       <c r="X88" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y88" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.2">
@@ -7370,10 +7370,10 @@
         <v>1.26</v>
       </c>
       <c r="X89" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y89" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.2">
@@ -7447,10 +7447,10 @@
         <v>1.26</v>
       </c>
       <c r="X90" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y90" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.2">
@@ -7524,10 +7524,10 @@
         <v>1.26</v>
       </c>
       <c r="X91" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y91" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.2">
@@ -7601,10 +7601,10 @@
         <v>1.26</v>
       </c>
       <c r="X92" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y92" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.2">
@@ -7678,10 +7678,10 @@
         <v>1.26</v>
       </c>
       <c r="X93" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y93" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.2">
@@ -7755,10 +7755,10 @@
         <v>1.26</v>
       </c>
       <c r="X94" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y94" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.2">
@@ -7832,10 +7832,10 @@
         <v>1.26</v>
       </c>
       <c r="X95" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y95" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.2">
@@ -7909,10 +7909,10 @@
         <v>1.26</v>
       </c>
       <c r="X96" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y96" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.2">
@@ -7986,10 +7986,10 @@
         <v>1.26</v>
       </c>
       <c r="X97" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y97" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.2">
@@ -8063,10 +8063,10 @@
         <v>1.26</v>
       </c>
       <c r="X98" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y98" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.2">
@@ -8140,10 +8140,10 @@
         <v>1.26</v>
       </c>
       <c r="X99" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y99" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.2">
@@ -8217,10 +8217,10 @@
         <v>1.26</v>
       </c>
       <c r="X100" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y100" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.2">
@@ -8294,10 +8294,10 @@
         <v>1.26</v>
       </c>
       <c r="X101" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y101" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:25" x14ac:dyDescent="0.2">
@@ -8371,10 +8371,10 @@
         <v>1.26</v>
       </c>
       <c r="X102" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y102" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="103" spans="1:25" x14ac:dyDescent="0.2">
@@ -8448,10 +8448,10 @@
         <v>1.26</v>
       </c>
       <c r="X103" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y103" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="104" spans="1:25" x14ac:dyDescent="0.2">
@@ -8525,10 +8525,10 @@
         <v>1.26</v>
       </c>
       <c r="X104" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y104" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="105" spans="1:25" x14ac:dyDescent="0.2">
@@ -8602,10 +8602,10 @@
         <v>1.26</v>
       </c>
       <c r="X105" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y105" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.2">
@@ -8679,10 +8679,10 @@
         <v>1.26</v>
       </c>
       <c r="X106" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y106" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="107" spans="1:25" x14ac:dyDescent="0.2">
@@ -8756,10 +8756,10 @@
         <v>1.26</v>
       </c>
       <c r="X107" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y107" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="108" spans="1:25" x14ac:dyDescent="0.2">
@@ -8833,10 +8833,10 @@
         <v>1.26</v>
       </c>
       <c r="X108" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y108" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="109" spans="1:25" x14ac:dyDescent="0.2">
@@ -8910,10 +8910,10 @@
         <v>1.26</v>
       </c>
       <c r="X109" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y109" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="110" spans="1:25" x14ac:dyDescent="0.2">
@@ -8987,10 +8987,10 @@
         <v>1.26</v>
       </c>
       <c r="X110" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y110" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:25" x14ac:dyDescent="0.2">
@@ -9064,10 +9064,10 @@
         <v>1.26</v>
       </c>
       <c r="X111" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y111" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.2">
@@ -9141,10 +9141,10 @@
         <v>1.26</v>
       </c>
       <c r="X112" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y112" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="113" spans="1:25" x14ac:dyDescent="0.2">
@@ -9218,10 +9218,10 @@
         <v>1.26</v>
       </c>
       <c r="X113" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y113" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="114" spans="1:25" x14ac:dyDescent="0.2">
@@ -9295,10 +9295,10 @@
         <v>1.26</v>
       </c>
       <c r="X114" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y114" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="115" spans="1:25" x14ac:dyDescent="0.2">
@@ -9372,10 +9372,10 @@
         <v>1.26</v>
       </c>
       <c r="X115" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y115" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="116" spans="1:25" x14ac:dyDescent="0.2">
@@ -9449,10 +9449,10 @@
         <v>1.26</v>
       </c>
       <c r="X116" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y116" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="117" spans="1:25" x14ac:dyDescent="0.2">
@@ -9526,10 +9526,10 @@
         <v>1.26</v>
       </c>
       <c r="X117" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y117" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="118" spans="1:25" x14ac:dyDescent="0.2">
@@ -9603,10 +9603,10 @@
         <v>1.26</v>
       </c>
       <c r="X118" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y118" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="119" spans="1:25" x14ac:dyDescent="0.2">
@@ -9680,10 +9680,10 @@
         <v>1.26</v>
       </c>
       <c r="X119" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y119" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="120" spans="1:25" x14ac:dyDescent="0.2">
@@ -9757,10 +9757,10 @@
         <v>1.26</v>
       </c>
       <c r="X120" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y120" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="121" spans="1:25" x14ac:dyDescent="0.2">
@@ -9834,10 +9834,10 @@
         <v>1.26</v>
       </c>
       <c r="X121" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y121" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="122" spans="1:25" x14ac:dyDescent="0.2">
@@ -9911,10 +9911,10 @@
         <v>1.26</v>
       </c>
       <c r="X122" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y122" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="123" spans="1:25" x14ac:dyDescent="0.2">
@@ -9988,10 +9988,10 @@
         <v>1.26</v>
       </c>
       <c r="X123" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y123" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="124" spans="1:25" x14ac:dyDescent="0.2">
@@ -10065,10 +10065,10 @@
         <v>1.26</v>
       </c>
       <c r="X124" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y124" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="125" spans="1:25" x14ac:dyDescent="0.2">
@@ -10142,10 +10142,10 @@
         <v>1.26</v>
       </c>
       <c r="X125" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y125" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="126" spans="1:25" x14ac:dyDescent="0.2">
@@ -10219,10 +10219,10 @@
         <v>1.26</v>
       </c>
       <c r="X126" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y126" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="127" spans="1:25" x14ac:dyDescent="0.2">
@@ -10296,10 +10296,10 @@
         <v>1.26</v>
       </c>
       <c r="X127" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y127" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="128" spans="1:25" x14ac:dyDescent="0.2">
@@ -10373,10 +10373,10 @@
         <v>1.26</v>
       </c>
       <c r="X128" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y128" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="129" spans="1:25" x14ac:dyDescent="0.2">
@@ -10450,10 +10450,10 @@
         <v>1.26</v>
       </c>
       <c r="X129" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y129" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="130" spans="1:25" x14ac:dyDescent="0.2">
@@ -10527,10 +10527,10 @@
         <v>1.26</v>
       </c>
       <c r="X130" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y130" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="131" spans="1:25" x14ac:dyDescent="0.2">
@@ -10604,10 +10604,10 @@
         <v>1.26</v>
       </c>
       <c r="X131" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y131" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.2">
@@ -10681,10 +10681,10 @@
         <v>1.26</v>
       </c>
       <c r="X132" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y132" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="133" spans="1:25" x14ac:dyDescent="0.2">
@@ -10758,10 +10758,10 @@
         <v>1.26</v>
       </c>
       <c r="X133" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y133" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="134" spans="1:25" x14ac:dyDescent="0.2">
@@ -10835,10 +10835,10 @@
         <v>1.26</v>
       </c>
       <c r="X134" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y134" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="135" spans="1:25" x14ac:dyDescent="0.2">
@@ -10912,10 +10912,10 @@
         <v>1.26</v>
       </c>
       <c r="X135" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y135" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="136" spans="1:25" x14ac:dyDescent="0.2">
@@ -10989,10 +10989,10 @@
         <v>1.26</v>
       </c>
       <c r="X136" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y136" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="137" spans="1:25" x14ac:dyDescent="0.2">
@@ -11066,10 +11066,10 @@
         <v>1.26</v>
       </c>
       <c r="X137" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y137" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="138" spans="1:25" x14ac:dyDescent="0.2">
@@ -11143,10 +11143,10 @@
         <v>1.26</v>
       </c>
       <c r="X138" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y138" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="139" spans="1:25" x14ac:dyDescent="0.2">
@@ -11220,10 +11220,10 @@
         <v>1.26</v>
       </c>
       <c r="X139" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y139" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="140" spans="1:25" x14ac:dyDescent="0.2">
@@ -11297,10 +11297,10 @@
         <v>1.26</v>
       </c>
       <c r="X140" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y140" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="141" spans="1:25" x14ac:dyDescent="0.2">
@@ -11374,10 +11374,10 @@
         <v>1.26</v>
       </c>
       <c r="X141" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y141" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="142" spans="1:25" x14ac:dyDescent="0.2">
@@ -11451,10 +11451,10 @@
         <v>1.26</v>
       </c>
       <c r="X142" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y142" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="143" spans="1:25" x14ac:dyDescent="0.2">
@@ -11528,10 +11528,10 @@
         <v>1.26</v>
       </c>
       <c r="X143" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y143" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="144" spans="1:25" x14ac:dyDescent="0.2">
@@ -11605,10 +11605,10 @@
         <v>1.26</v>
       </c>
       <c r="X144" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y144" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="145" spans="1:25" x14ac:dyDescent="0.2">
@@ -11682,10 +11682,10 @@
         <v>1.26</v>
       </c>
       <c r="X145" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y145" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="146" spans="1:25" x14ac:dyDescent="0.2">
@@ -11759,10 +11759,10 @@
         <v>1.26</v>
       </c>
       <c r="X146" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y146" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="147" spans="1:25" x14ac:dyDescent="0.2">
@@ -11836,10 +11836,10 @@
         <v>1.26</v>
       </c>
       <c r="X147" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y147" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="148" spans="1:25" x14ac:dyDescent="0.2">
@@ -11913,10 +11913,10 @@
         <v>1.26</v>
       </c>
       <c r="X148" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y148" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="149" spans="1:25" x14ac:dyDescent="0.2">
@@ -11990,10 +11990,10 @@
         <v>1.26</v>
       </c>
       <c r="X149" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y149" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="150" spans="1:25" x14ac:dyDescent="0.2">
@@ -12067,10 +12067,10 @@
         <v>1.26</v>
       </c>
       <c r="X150" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y150" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="151" spans="1:25" x14ac:dyDescent="0.2">
@@ -12144,10 +12144,10 @@
         <v>1.26</v>
       </c>
       <c r="X151" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y151" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="152" spans="1:25" x14ac:dyDescent="0.2">
@@ -12221,10 +12221,10 @@
         <v>1.26</v>
       </c>
       <c r="X152" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y152" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="153" spans="1:25" x14ac:dyDescent="0.2">
@@ -12298,10 +12298,10 @@
         <v>1.26</v>
       </c>
       <c r="X153" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y153" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="154" spans="1:25" x14ac:dyDescent="0.2">
@@ -12375,10 +12375,10 @@
         <v>1.26</v>
       </c>
       <c r="X154" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y154" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="155" spans="1:25" x14ac:dyDescent="0.2">
@@ -12452,10 +12452,10 @@
         <v>1.26</v>
       </c>
       <c r="X155" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y155" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="156" spans="1:25" x14ac:dyDescent="0.2">
@@ -12529,10 +12529,10 @@
         <v>1.26</v>
       </c>
       <c r="X156" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y156" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="157" spans="1:25" x14ac:dyDescent="0.2">
@@ -12606,10 +12606,10 @@
         <v>1.26</v>
       </c>
       <c r="X157" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y157" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="158" spans="1:25" x14ac:dyDescent="0.2">
@@ -12683,10 +12683,10 @@
         <v>1.26</v>
       </c>
       <c r="X158" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y158" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="159" spans="1:25" x14ac:dyDescent="0.2">
@@ -12760,10 +12760,10 @@
         <v>1.26</v>
       </c>
       <c r="X159" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y159" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="160" spans="1:25" x14ac:dyDescent="0.2">
@@ -12837,10 +12837,10 @@
         <v>1.26</v>
       </c>
       <c r="X160" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y160" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="161" spans="1:25" x14ac:dyDescent="0.2">
@@ -12914,10 +12914,10 @@
         <v>1.26</v>
       </c>
       <c r="X161" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y161" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="162" spans="1:25" x14ac:dyDescent="0.2">
@@ -12991,10 +12991,10 @@
         <v>1.26</v>
       </c>
       <c r="X162" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y162" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="163" spans="1:25" x14ac:dyDescent="0.2">
@@ -13068,10 +13068,10 @@
         <v>1.26</v>
       </c>
       <c r="X163" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y163" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="164" spans="1:25" x14ac:dyDescent="0.2">
@@ -13145,10 +13145,10 @@
         <v>1.26</v>
       </c>
       <c r="X164" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y164" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="165" spans="1:25" x14ac:dyDescent="0.2">
@@ -13222,10 +13222,10 @@
         <v>1.26</v>
       </c>
       <c r="X165" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y165" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="166" spans="1:25" x14ac:dyDescent="0.2">
@@ -13299,10 +13299,10 @@
         <v>1.26</v>
       </c>
       <c r="X166" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y166" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="167" spans="1:25" x14ac:dyDescent="0.2">
@@ -13376,10 +13376,10 @@
         <v>1.26</v>
       </c>
       <c r="X167" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y167" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="168" spans="1:25" x14ac:dyDescent="0.2">
@@ -13453,10 +13453,10 @@
         <v>1.26</v>
       </c>
       <c r="X168" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y168" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="169" spans="1:25" x14ac:dyDescent="0.2">
@@ -13530,10 +13530,10 @@
         <v>1.26</v>
       </c>
       <c r="X169" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y169" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="170" spans="1:25" x14ac:dyDescent="0.2">
@@ -13607,10 +13607,10 @@
         <v>1.26</v>
       </c>
       <c r="X170" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y170" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="171" spans="1:25" x14ac:dyDescent="0.2">
@@ -13684,10 +13684,10 @@
         <v>1.26</v>
       </c>
       <c r="X171" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y171" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="172" spans="1:25" x14ac:dyDescent="0.2">
@@ -13761,10 +13761,10 @@
         <v>1.26</v>
       </c>
       <c r="X172" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y172" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="173" spans="1:25" x14ac:dyDescent="0.2">
@@ -13838,10 +13838,10 @@
         <v>1.26</v>
       </c>
       <c r="X173" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y173" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="174" spans="1:25" x14ac:dyDescent="0.2">
@@ -13915,10 +13915,10 @@
         <v>1.26</v>
       </c>
       <c r="X174" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y174" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="175" spans="1:25" x14ac:dyDescent="0.2">
@@ -13992,10 +13992,10 @@
         <v>1.26</v>
       </c>
       <c r="X175" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y175" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="176" spans="1:25" x14ac:dyDescent="0.2">
@@ -14069,10 +14069,10 @@
         <v>1.26</v>
       </c>
       <c r="X176" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y176" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="177" spans="1:25" x14ac:dyDescent="0.2">
@@ -14146,10 +14146,10 @@
         <v>1.26</v>
       </c>
       <c r="X177" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y177" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="178" spans="1:25" x14ac:dyDescent="0.2">
@@ -14223,10 +14223,10 @@
         <v>1.26</v>
       </c>
       <c r="X178" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y178" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="179" spans="1:25" x14ac:dyDescent="0.2">
@@ -14300,10 +14300,10 @@
         <v>1.26</v>
       </c>
       <c r="X179" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y179" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="180" spans="1:25" x14ac:dyDescent="0.2">
@@ -14377,10 +14377,10 @@
         <v>1.26</v>
       </c>
       <c r="X180" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y180" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="181" spans="1:25" x14ac:dyDescent="0.2">
@@ -14454,10 +14454,10 @@
         <v>1.26</v>
       </c>
       <c r="X181" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y181" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:25" x14ac:dyDescent="0.2">
@@ -14531,10 +14531,10 @@
         <v>1.26</v>
       </c>
       <c r="X182" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y182" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="183" spans="1:25" x14ac:dyDescent="0.2">
@@ -14608,10 +14608,10 @@
         <v>1.26</v>
       </c>
       <c r="X183" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y183" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="184" spans="1:25" x14ac:dyDescent="0.2">
@@ -14685,10 +14685,10 @@
         <v>1.26</v>
       </c>
       <c r="X184" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y184" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="185" spans="1:25" x14ac:dyDescent="0.2">
@@ -14762,10 +14762,10 @@
         <v>1.26</v>
       </c>
       <c r="X185" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y185" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="186" spans="1:25" x14ac:dyDescent="0.2">
@@ -14839,10 +14839,10 @@
         <v>1.26</v>
       </c>
       <c r="X186" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y186" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="187" spans="1:25" x14ac:dyDescent="0.2">
@@ -14916,10 +14916,10 @@
         <v>1.26</v>
       </c>
       <c r="X187" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y187" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="188" spans="1:25" x14ac:dyDescent="0.2">
@@ -14993,10 +14993,10 @@
         <v>1.26</v>
       </c>
       <c r="X188" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y188" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="189" spans="1:25" x14ac:dyDescent="0.2">
@@ -15070,10 +15070,10 @@
         <v>1.26</v>
       </c>
       <c r="X189" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y189" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="190" spans="1:25" x14ac:dyDescent="0.2">
@@ -15147,10 +15147,10 @@
         <v>1.26</v>
       </c>
       <c r="X190" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y190" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="191" spans="1:25" x14ac:dyDescent="0.2">
@@ -15224,10 +15224,10 @@
         <v>1.26</v>
       </c>
       <c r="X191" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y191" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="192" spans="1:25" x14ac:dyDescent="0.2">
@@ -15301,10 +15301,10 @@
         <v>1.26</v>
       </c>
       <c r="X192" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y192" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="193" spans="1:25" x14ac:dyDescent="0.2">
@@ -15378,10 +15378,10 @@
         <v>1.26</v>
       </c>
       <c r="X193" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y193" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="194" spans="1:25" x14ac:dyDescent="0.2">
@@ -15455,10 +15455,10 @@
         <v>1.26</v>
       </c>
       <c r="X194" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y194" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="195" spans="1:25" x14ac:dyDescent="0.2">
@@ -15532,10 +15532,10 @@
         <v>1.26</v>
       </c>
       <c r="X195" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y195" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="196" spans="1:25" x14ac:dyDescent="0.2">
@@ -15609,10 +15609,10 @@
         <v>1.26</v>
       </c>
       <c r="X196" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y196" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="197" spans="1:25" x14ac:dyDescent="0.2">
@@ -15686,10 +15686,10 @@
         <v>1.26</v>
       </c>
       <c r="X197" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y197" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="198" spans="1:25" x14ac:dyDescent="0.2">
@@ -15763,10 +15763,10 @@
         <v>1.26</v>
       </c>
       <c r="X198" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y198" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="199" spans="1:25" x14ac:dyDescent="0.2">
@@ -15840,10 +15840,10 @@
         <v>1.26</v>
       </c>
       <c r="X199" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y199" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="200" spans="1:25" x14ac:dyDescent="0.2">
@@ -15917,10 +15917,10 @@
         <v>1.26</v>
       </c>
       <c r="X200" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y200" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="201" spans="1:25" x14ac:dyDescent="0.2">
@@ -15994,10 +15994,10 @@
         <v>1.26</v>
       </c>
       <c r="X201" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y201" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="202" spans="1:25" x14ac:dyDescent="0.2">
@@ -16071,10 +16071,10 @@
         <v>1.26</v>
       </c>
       <c r="X202" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y202" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="203" spans="1:25" x14ac:dyDescent="0.2">
@@ -16148,10 +16148,10 @@
         <v>1.26</v>
       </c>
       <c r="X203" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y203" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="204" spans="1:25" x14ac:dyDescent="0.2">
@@ -16225,10 +16225,10 @@
         <v>1.26</v>
       </c>
       <c r="X204" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y204" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="205" spans="1:25" x14ac:dyDescent="0.2">
@@ -16302,10 +16302,10 @@
         <v>1.26</v>
       </c>
       <c r="X205" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y205" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="206" spans="1:25" x14ac:dyDescent="0.2">
@@ -16379,10 +16379,10 @@
         <v>1.26</v>
       </c>
       <c r="X206" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y206" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="207" spans="1:25" x14ac:dyDescent="0.2">
@@ -16456,10 +16456,10 @@
         <v>1.26</v>
       </c>
       <c r="X207" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y207" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="208" spans="1:25" x14ac:dyDescent="0.2">
@@ -16533,10 +16533,10 @@
         <v>1.26</v>
       </c>
       <c r="X208" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y208" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="209" spans="1:25" x14ac:dyDescent="0.2">
@@ -16610,10 +16610,10 @@
         <v>1.26</v>
       </c>
       <c r="X209" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y209" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="210" spans="1:25" x14ac:dyDescent="0.2">
@@ -16687,10 +16687,10 @@
         <v>1.26</v>
       </c>
       <c r="X210" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y210" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="211" spans="1:25" x14ac:dyDescent="0.2">
@@ -16764,10 +16764,10 @@
         <v>1.26</v>
       </c>
       <c r="X211" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y211" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="212" spans="1:25" x14ac:dyDescent="0.2">
@@ -16841,10 +16841,10 @@
         <v>1.26</v>
       </c>
       <c r="X212" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y212" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="213" spans="1:25" x14ac:dyDescent="0.2">
@@ -16918,10 +16918,10 @@
         <v>1.26</v>
       </c>
       <c r="X213" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y213" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="214" spans="1:25" x14ac:dyDescent="0.2">
@@ -16995,10 +16995,10 @@
         <v>1.26</v>
       </c>
       <c r="X214" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y214" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="215" spans="1:25" x14ac:dyDescent="0.2">
@@ -17072,10 +17072,10 @@
         <v>1.26</v>
       </c>
       <c r="X215" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y215" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="216" spans="1:25" x14ac:dyDescent="0.2">
@@ -17149,10 +17149,10 @@
         <v>1.26</v>
       </c>
       <c r="X216" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y216" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="217" spans="1:25" x14ac:dyDescent="0.2">
@@ -17226,10 +17226,10 @@
         <v>1.26</v>
       </c>
       <c r="X217" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y217" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="218" spans="1:25" x14ac:dyDescent="0.2">
@@ -17303,10 +17303,10 @@
         <v>1.26</v>
       </c>
       <c r="X218" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y218" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="219" spans="1:25" x14ac:dyDescent="0.2">
@@ -17380,10 +17380,10 @@
         <v>1.26</v>
       </c>
       <c r="X219" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y219" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="220" spans="1:25" x14ac:dyDescent="0.2">
@@ -17457,10 +17457,10 @@
         <v>1.26</v>
       </c>
       <c r="X220" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y220" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="221" spans="1:25" x14ac:dyDescent="0.2">
@@ -17534,10 +17534,10 @@
         <v>1.26</v>
       </c>
       <c r="X221" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y221" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="222" spans="1:25" x14ac:dyDescent="0.2">
@@ -17611,10 +17611,10 @@
         <v>1.26</v>
       </c>
       <c r="X222" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y222" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="223" spans="1:25" x14ac:dyDescent="0.2">
@@ -17688,10 +17688,10 @@
         <v>1.26</v>
       </c>
       <c r="X223" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y223" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="224" spans="1:25" x14ac:dyDescent="0.2">
@@ -17765,10 +17765,10 @@
         <v>1.26</v>
       </c>
       <c r="X224" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y224" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="225" spans="1:25" x14ac:dyDescent="0.2">
@@ -17842,10 +17842,10 @@
         <v>1.26</v>
       </c>
       <c r="X225" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y225" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="226" spans="1:25" x14ac:dyDescent="0.2">
@@ -17919,10 +17919,10 @@
         <v>1.26</v>
       </c>
       <c r="X226" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y226" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="227" spans="1:25" x14ac:dyDescent="0.2">
@@ -17996,10 +17996,10 @@
         <v>1.26</v>
       </c>
       <c r="X227" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y227" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="228" spans="1:25" x14ac:dyDescent="0.2">
@@ -18073,10 +18073,10 @@
         <v>1.26</v>
       </c>
       <c r="X228" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y228" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="229" spans="1:25" x14ac:dyDescent="0.2">
@@ -18150,10 +18150,10 @@
         <v>1.26</v>
       </c>
       <c r="X229" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y229" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="230" spans="1:25" x14ac:dyDescent="0.2">
@@ -18227,10 +18227,10 @@
         <v>1.26</v>
       </c>
       <c r="X230" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y230" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="231" spans="1:25" x14ac:dyDescent="0.2">
@@ -18304,10 +18304,10 @@
         <v>1.26</v>
       </c>
       <c r="X231" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y231" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="232" spans="1:25" x14ac:dyDescent="0.2">
@@ -18381,10 +18381,10 @@
         <v>1.26</v>
       </c>
       <c r="X232" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y232" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="233" spans="1:25" x14ac:dyDescent="0.2">
@@ -18458,10 +18458,10 @@
         <v>1.26</v>
       </c>
       <c r="X233" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y233" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="234" spans="1:25" x14ac:dyDescent="0.2">
@@ -18535,10 +18535,10 @@
         <v>1.26</v>
       </c>
       <c r="X234" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y234" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="235" spans="1:25" x14ac:dyDescent="0.2">
@@ -18612,10 +18612,10 @@
         <v>1.26</v>
       </c>
       <c r="X235" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y235" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="236" spans="1:25" x14ac:dyDescent="0.2">
@@ -18689,10 +18689,10 @@
         <v>1.26</v>
       </c>
       <c r="X236" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y236" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="237" spans="1:25" x14ac:dyDescent="0.2">
@@ -18766,10 +18766,10 @@
         <v>1.26</v>
       </c>
       <c r="X237" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y237" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="238" spans="1:25" x14ac:dyDescent="0.2">
@@ -18843,10 +18843,10 @@
         <v>1.26</v>
       </c>
       <c r="X238" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y238" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="239" spans="1:25" x14ac:dyDescent="0.2">
@@ -18920,10 +18920,10 @@
         <v>1.26</v>
       </c>
       <c r="X239" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y239" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="240" spans="1:25" x14ac:dyDescent="0.2">
@@ -18997,10 +18997,10 @@
         <v>1.26</v>
       </c>
       <c r="X240" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y240" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="241" spans="1:25" x14ac:dyDescent="0.2">
@@ -19074,10 +19074,10 @@
         <v>1.26</v>
       </c>
       <c r="X241" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y241" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="242" spans="1:25" x14ac:dyDescent="0.2">
@@ -19151,10 +19151,10 @@
         <v>1.26</v>
       </c>
       <c r="X242" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y242" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="243" spans="1:25" x14ac:dyDescent="0.2">
@@ -19228,10 +19228,10 @@
         <v>1.26</v>
       </c>
       <c r="X243" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y243" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="244" spans="1:25" x14ac:dyDescent="0.2">
@@ -19305,10 +19305,10 @@
         <v>1.26</v>
       </c>
       <c r="X244" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y244" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="245" spans="1:25" x14ac:dyDescent="0.2">
@@ -19382,10 +19382,10 @@
         <v>1.26</v>
       </c>
       <c r="X245" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y245" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="246" spans="1:25" x14ac:dyDescent="0.2">
@@ -19459,10 +19459,10 @@
         <v>1.26</v>
       </c>
       <c r="X246" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y246" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="247" spans="1:25" x14ac:dyDescent="0.2">
@@ -19536,10 +19536,10 @@
         <v>1.26</v>
       </c>
       <c r="X247" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y247" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="248" spans="1:25" x14ac:dyDescent="0.2">
@@ -19613,10 +19613,10 @@
         <v>1.26</v>
       </c>
       <c r="X248" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y248" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="249" spans="1:25" x14ac:dyDescent="0.2">
@@ -19690,10 +19690,10 @@
         <v>1.26</v>
       </c>
       <c r="X249" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y249" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="250" spans="1:25" x14ac:dyDescent="0.2">
@@ -19767,10 +19767,10 @@
         <v>1.26</v>
       </c>
       <c r="X250" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y250" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="251" spans="1:25" x14ac:dyDescent="0.2">
@@ -19844,10 +19844,10 @@
         <v>1.26</v>
       </c>
       <c r="X251" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y251" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="252" spans="1:25" x14ac:dyDescent="0.2">
@@ -19921,10 +19921,10 @@
         <v>1.26</v>
       </c>
       <c r="X252" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y252" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="253" spans="1:25" x14ac:dyDescent="0.2">
@@ -19998,10 +19998,10 @@
         <v>1.26</v>
       </c>
       <c r="X253" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y253" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="254" spans="1:25" x14ac:dyDescent="0.2">
@@ -20075,10 +20075,10 @@
         <v>1.26</v>
       </c>
       <c r="X254" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y254" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="255" spans="1:25" x14ac:dyDescent="0.2">
@@ -20152,10 +20152,10 @@
         <v>1.26</v>
       </c>
       <c r="X255" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y255" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="256" spans="1:25" x14ac:dyDescent="0.2">
@@ -20229,10 +20229,10 @@
         <v>1.26</v>
       </c>
       <c r="X256" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y256" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="257" spans="1:25" x14ac:dyDescent="0.2">
@@ -20306,10 +20306,10 @@
         <v>1.26</v>
       </c>
       <c r="X257" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y257" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="258" spans="1:25" x14ac:dyDescent="0.2">
@@ -20383,10 +20383,10 @@
         <v>1.26</v>
       </c>
       <c r="X258" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y258" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="259" spans="1:25" x14ac:dyDescent="0.2">
@@ -20460,10 +20460,10 @@
         <v>1.26</v>
       </c>
       <c r="X259" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y259" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="260" spans="1:25" x14ac:dyDescent="0.2">
@@ -20537,10 +20537,10 @@
         <v>1.26</v>
       </c>
       <c r="X260" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y260" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="261" spans="1:25" x14ac:dyDescent="0.2">
@@ -20614,10 +20614,10 @@
         <v>1.26</v>
       </c>
       <c r="X261" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y261" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="262" spans="1:25" x14ac:dyDescent="0.2">
@@ -20691,10 +20691,10 @@
         <v>1.26</v>
       </c>
       <c r="X262" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y262" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="263" spans="1:25" x14ac:dyDescent="0.2">
@@ -20768,10 +20768,10 @@
         <v>1.26</v>
       </c>
       <c r="X263" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y263" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="264" spans="1:25" x14ac:dyDescent="0.2">
@@ -20845,10 +20845,10 @@
         <v>1.26</v>
       </c>
       <c r="X264" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y264" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="265" spans="1:25" x14ac:dyDescent="0.2">
@@ -20922,10 +20922,10 @@
         <v>1.26</v>
       </c>
       <c r="X265" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y265" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="266" spans="1:25" x14ac:dyDescent="0.2">
@@ -20999,10 +20999,10 @@
         <v>1.26</v>
       </c>
       <c r="X266" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y266" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="267" spans="1:25" x14ac:dyDescent="0.2">
@@ -21076,10 +21076,10 @@
         <v>1.26</v>
       </c>
       <c r="X267" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y267" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="268" spans="1:25" x14ac:dyDescent="0.2">
@@ -21153,10 +21153,10 @@
         <v>1.26</v>
       </c>
       <c r="X268" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y268" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="269" spans="1:25" x14ac:dyDescent="0.2">
@@ -21230,10 +21230,10 @@
         <v>1.26</v>
       </c>
       <c r="X269" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y269" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="270" spans="1:25" x14ac:dyDescent="0.2">
@@ -21307,10 +21307,10 @@
         <v>1.26</v>
       </c>
       <c r="X270" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y270" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="271" spans="1:25" x14ac:dyDescent="0.2">
@@ -21384,10 +21384,10 @@
         <v>1.26</v>
       </c>
       <c r="X271" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y271" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="272" spans="1:25" x14ac:dyDescent="0.2">
@@ -21461,10 +21461,10 @@
         <v>1.26</v>
       </c>
       <c r="X272" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y272" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="273" spans="1:25" x14ac:dyDescent="0.2">
@@ -21538,10 +21538,10 @@
         <v>1.26</v>
       </c>
       <c r="X273" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y273" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="274" spans="1:25" x14ac:dyDescent="0.2">
@@ -21615,10 +21615,10 @@
         <v>1.26</v>
       </c>
       <c r="X274" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y274" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="275" spans="1:25" x14ac:dyDescent="0.2">
@@ -21692,10 +21692,10 @@
         <v>1.26</v>
       </c>
       <c r="X275" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y275" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="276" spans="1:25" x14ac:dyDescent="0.2">
@@ -21769,10 +21769,10 @@
         <v>1.26</v>
       </c>
       <c r="X276" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y276" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="277" spans="1:25" x14ac:dyDescent="0.2">
@@ -21846,10 +21846,10 @@
         <v>1.26</v>
       </c>
       <c r="X277" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y277" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="278" spans="1:25" x14ac:dyDescent="0.2">
@@ -21923,10 +21923,10 @@
         <v>1.26</v>
       </c>
       <c r="X278" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y278" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="279" spans="1:25" x14ac:dyDescent="0.2">
@@ -22000,10 +22000,10 @@
         <v>1.26</v>
       </c>
       <c r="X279" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y279" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="280" spans="1:25" x14ac:dyDescent="0.2">
@@ -22077,10 +22077,10 @@
         <v>1.26</v>
       </c>
       <c r="X280" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y280" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="281" spans="1:25" x14ac:dyDescent="0.2">
@@ -22154,10 +22154,10 @@
         <v>1.26</v>
       </c>
       <c r="X281" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y281" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="282" spans="1:25" x14ac:dyDescent="0.2">
@@ -22231,10 +22231,10 @@
         <v>1.26</v>
       </c>
       <c r="X282" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y282" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="283" spans="1:25" x14ac:dyDescent="0.2">
@@ -22308,10 +22308,10 @@
         <v>1.26</v>
       </c>
       <c r="X283" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y283" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="284" spans="1:25" x14ac:dyDescent="0.2">
@@ -22385,10 +22385,10 @@
         <v>1.26</v>
       </c>
       <c r="X284" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y284" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="285" spans="1:25" x14ac:dyDescent="0.2">
@@ -22462,10 +22462,10 @@
         <v>1.26</v>
       </c>
       <c r="X285" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y285" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="286" spans="1:25" x14ac:dyDescent="0.2">
@@ -22539,10 +22539,10 @@
         <v>1.26</v>
       </c>
       <c r="X286" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y286" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="287" spans="1:25" x14ac:dyDescent="0.2">
@@ -22616,10 +22616,10 @@
         <v>1.26</v>
       </c>
       <c r="X287" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y287" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="288" spans="1:25" x14ac:dyDescent="0.2">
@@ -22693,10 +22693,10 @@
         <v>1.26</v>
       </c>
       <c r="X288" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y288" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="289" spans="1:25" x14ac:dyDescent="0.2">
@@ -22770,10 +22770,10 @@
         <v>1.26</v>
       </c>
       <c r="X289" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y289" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="290" spans="1:25" x14ac:dyDescent="0.2">
@@ -22847,10 +22847,10 @@
         <v>1.26</v>
       </c>
       <c r="X290" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y290" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="291" spans="1:25" x14ac:dyDescent="0.2">
@@ -22924,10 +22924,10 @@
         <v>1.26</v>
       </c>
       <c r="X291" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y291" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="292" spans="1:25" x14ac:dyDescent="0.2">
@@ -23001,10 +23001,10 @@
         <v>1.26</v>
       </c>
       <c r="X292" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y292" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="293" spans="1:25" x14ac:dyDescent="0.2">
@@ -23078,10 +23078,10 @@
         <v>1.26</v>
       </c>
       <c r="X293" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y293" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="294" spans="1:25" x14ac:dyDescent="0.2">
@@ -23155,10 +23155,10 @@
         <v>1.26</v>
       </c>
       <c r="X294" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y294" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="295" spans="1:25" x14ac:dyDescent="0.2">
@@ -23232,10 +23232,10 @@
         <v>1.26</v>
       </c>
       <c r="X295" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y295" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="296" spans="1:25" x14ac:dyDescent="0.2">
@@ -23309,10 +23309,10 @@
         <v>1.26</v>
       </c>
       <c r="X296" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y296" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="297" spans="1:25" x14ac:dyDescent="0.2">
@@ -23386,10 +23386,10 @@
         <v>1.26</v>
       </c>
       <c r="X297" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y297" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="298" spans="1:25" x14ac:dyDescent="0.2">
@@ -23463,10 +23463,10 @@
         <v>1.26</v>
       </c>
       <c r="X298" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y298" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="299" spans="1:25" x14ac:dyDescent="0.2">
@@ -23540,10 +23540,10 @@
         <v>1.26</v>
       </c>
       <c r="X299" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y299" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="300" spans="1:25" x14ac:dyDescent="0.2">
@@ -23617,10 +23617,10 @@
         <v>1.26</v>
       </c>
       <c r="X300" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y300" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="301" spans="1:25" x14ac:dyDescent="0.2">
@@ -23694,10 +23694,10 @@
         <v>1.26</v>
       </c>
       <c r="X301" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y301" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="302" spans="1:25" x14ac:dyDescent="0.2">
@@ -23771,10 +23771,10 @@
         <v>1.26</v>
       </c>
       <c r="X302" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y302" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="303" spans="1:25" x14ac:dyDescent="0.2">
@@ -23848,10 +23848,10 @@
         <v>1.26</v>
       </c>
       <c r="X303" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y303" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="304" spans="1:25" x14ac:dyDescent="0.2">
@@ -23925,10 +23925,10 @@
         <v>1.26</v>
       </c>
       <c r="X304" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y304" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="305" spans="1:25" x14ac:dyDescent="0.2">
@@ -24002,10 +24002,10 @@
         <v>1.26</v>
       </c>
       <c r="X305" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y305" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="306" spans="1:25" x14ac:dyDescent="0.2">
@@ -24079,10 +24079,10 @@
         <v>1.26</v>
       </c>
       <c r="X306" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y306" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="307" spans="1:25" x14ac:dyDescent="0.2">
@@ -24156,10 +24156,10 @@
         <v>1.26</v>
       </c>
       <c r="X307" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y307" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="308" spans="1:25" x14ac:dyDescent="0.2">
@@ -24233,10 +24233,10 @@
         <v>1.26</v>
       </c>
       <c r="X308" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y308" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="309" spans="1:25" x14ac:dyDescent="0.2">
@@ -24310,10 +24310,10 @@
         <v>1.26</v>
       </c>
       <c r="X309" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y309" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="310" spans="1:25" x14ac:dyDescent="0.2">
@@ -24387,10 +24387,10 @@
         <v>1.26</v>
       </c>
       <c r="X310" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y310" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="311" spans="1:25" x14ac:dyDescent="0.2">
@@ -24464,10 +24464,10 @@
         <v>1.26</v>
       </c>
       <c r="X311" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y311" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="312" spans="1:25" x14ac:dyDescent="0.2">
@@ -24541,10 +24541,10 @@
         <v>1.26</v>
       </c>
       <c r="X312" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y312" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="313" spans="1:25" x14ac:dyDescent="0.2">
@@ -24618,10 +24618,10 @@
         <v>1.26</v>
       </c>
       <c r="X313" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y313" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="314" spans="1:25" x14ac:dyDescent="0.2">
@@ -24695,10 +24695,10 @@
         <v>1.26</v>
       </c>
       <c r="X314" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y314" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="315" spans="1:25" x14ac:dyDescent="0.2">
@@ -24772,10 +24772,10 @@
         <v>1.26</v>
       </c>
       <c r="X315" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y315" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="316" spans="1:25" x14ac:dyDescent="0.2">
@@ -24849,10 +24849,10 @@
         <v>1.26</v>
       </c>
       <c r="X316" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y316" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="317" spans="1:25" x14ac:dyDescent="0.2">
@@ -24926,10 +24926,10 @@
         <v>1.26</v>
       </c>
       <c r="X317" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y317" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="318" spans="1:25" x14ac:dyDescent="0.2">
@@ -25003,10 +25003,10 @@
         <v>1.26</v>
       </c>
       <c r="X318" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y318" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="319" spans="1:25" x14ac:dyDescent="0.2">
@@ -25080,10 +25080,10 @@
         <v>1.26</v>
       </c>
       <c r="X319" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y319" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="320" spans="1:25" x14ac:dyDescent="0.2">
@@ -25157,10 +25157,10 @@
         <v>1.26</v>
       </c>
       <c r="X320" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y320" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="321" spans="1:25" x14ac:dyDescent="0.2">
@@ -25234,10 +25234,10 @@
         <v>1.26</v>
       </c>
       <c r="X321" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y321" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="322" spans="1:25" x14ac:dyDescent="0.2">
@@ -25311,10 +25311,10 @@
         <v>1.26</v>
       </c>
       <c r="X322" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y322" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="323" spans="1:25" x14ac:dyDescent="0.2">
@@ -25388,10 +25388,10 @@
         <v>1.26</v>
       </c>
       <c r="X323" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y323" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="324" spans="1:25" x14ac:dyDescent="0.2">
@@ -25465,10 +25465,10 @@
         <v>1.26</v>
       </c>
       <c r="X324" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y324" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="325" spans="1:25" x14ac:dyDescent="0.2">
@@ -25542,10 +25542,10 @@
         <v>1.26</v>
       </c>
       <c r="X325" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y325" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="326" spans="1:25" x14ac:dyDescent="0.2">
@@ -25619,10 +25619,10 @@
         <v>1.26</v>
       </c>
       <c r="X326" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y326" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="327" spans="1:25" x14ac:dyDescent="0.2">
@@ -25696,10 +25696,10 @@
         <v>1.26</v>
       </c>
       <c r="X327" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y327" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="328" spans="1:25" x14ac:dyDescent="0.2">
@@ -25773,10 +25773,10 @@
         <v>1.26</v>
       </c>
       <c r="X328" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y328" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="329" spans="1:25" x14ac:dyDescent="0.2">
@@ -25850,10 +25850,10 @@
         <v>1.26</v>
       </c>
       <c r="X329" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y329" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="330" spans="1:25" x14ac:dyDescent="0.2">
@@ -25927,10 +25927,10 @@
         <v>1.26</v>
       </c>
       <c r="X330" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y330" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="331" spans="1:25" x14ac:dyDescent="0.2">
@@ -26004,10 +26004,10 @@
         <v>1.26</v>
       </c>
       <c r="X331" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y331" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="332" spans="1:25" x14ac:dyDescent="0.2">
@@ -26081,10 +26081,10 @@
         <v>1.26</v>
       </c>
       <c r="X332" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y332" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="333" spans="1:25" x14ac:dyDescent="0.2">
@@ -26158,10 +26158,10 @@
         <v>1.26</v>
       </c>
       <c r="X333" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y333" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="334" spans="1:25" x14ac:dyDescent="0.2">
@@ -26235,10 +26235,10 @@
         <v>1.26</v>
       </c>
       <c r="X334" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y334" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="335" spans="1:25" x14ac:dyDescent="0.2">
@@ -26312,10 +26312,10 @@
         <v>1.26</v>
       </c>
       <c r="X335" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y335" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="336" spans="1:25" x14ac:dyDescent="0.2">
@@ -26389,10 +26389,10 @@
         <v>1.26</v>
       </c>
       <c r="X336" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y336" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="337" spans="1:25" x14ac:dyDescent="0.2">
@@ -26466,10 +26466,10 @@
         <v>1.26</v>
       </c>
       <c r="X337" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y337" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="338" spans="1:25" x14ac:dyDescent="0.2">
@@ -26543,10 +26543,10 @@
         <v>1.26</v>
       </c>
       <c r="X338" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y338" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="339" spans="1:25" x14ac:dyDescent="0.2">
@@ -26620,10 +26620,10 @@
         <v>1.26</v>
       </c>
       <c r="X339" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y339" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="340" spans="1:25" x14ac:dyDescent="0.2">
@@ -26697,10 +26697,10 @@
         <v>1.26</v>
       </c>
       <c r="X340" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y340" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="341" spans="1:25" x14ac:dyDescent="0.2">
@@ -26774,10 +26774,10 @@
         <v>1.26</v>
       </c>
       <c r="X341" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y341" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="342" spans="1:25" x14ac:dyDescent="0.2">
@@ -26851,10 +26851,10 @@
         <v>1.26</v>
       </c>
       <c r="X342" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y342" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="343" spans="1:25" x14ac:dyDescent="0.2">
@@ -26928,10 +26928,10 @@
         <v>1.26</v>
       </c>
       <c r="X343" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y343" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="344" spans="1:25" x14ac:dyDescent="0.2">
@@ -27005,10 +27005,10 @@
         <v>1.26</v>
       </c>
       <c r="X344" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y344" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="345" spans="1:25" x14ac:dyDescent="0.2">
@@ -27082,10 +27082,10 @@
         <v>1.26</v>
       </c>
       <c r="X345" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y345" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="346" spans="1:25" x14ac:dyDescent="0.2">
@@ -27159,10 +27159,10 @@
         <v>1.26</v>
       </c>
       <c r="X346" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y346" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="347" spans="1:25" x14ac:dyDescent="0.2">
@@ -27236,10 +27236,10 @@
         <v>1.26</v>
       </c>
       <c r="X347" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y347" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="348" spans="1:25" x14ac:dyDescent="0.2">
@@ -27313,10 +27313,10 @@
         <v>1.26</v>
       </c>
       <c r="X348" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y348" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="349" spans="1:25" x14ac:dyDescent="0.2">
@@ -27390,10 +27390,10 @@
         <v>1.26</v>
       </c>
       <c r="X349" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y349" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="350" spans="1:25" x14ac:dyDescent="0.2">
@@ -27467,10 +27467,10 @@
         <v>1.26</v>
       </c>
       <c r="X350" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y350" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="351" spans="1:25" x14ac:dyDescent="0.2">
@@ -27544,10 +27544,10 @@
         <v>1.26</v>
       </c>
       <c r="X351" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y351" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="352" spans="1:25" x14ac:dyDescent="0.2">
@@ -27621,10 +27621,10 @@
         <v>1.26</v>
       </c>
       <c r="X352" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y352" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="353" spans="1:25" x14ac:dyDescent="0.2">
@@ -27698,10 +27698,10 @@
         <v>1.26</v>
       </c>
       <c r="X353" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y353" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="354" spans="1:25" x14ac:dyDescent="0.2">
@@ -27775,10 +27775,10 @@
         <v>1.26</v>
       </c>
       <c r="X354" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y354" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="355" spans="1:25" x14ac:dyDescent="0.2">
@@ -27852,10 +27852,10 @@
         <v>1.26</v>
       </c>
       <c r="X355" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y355" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="356" spans="1:25" x14ac:dyDescent="0.2">
@@ -27929,10 +27929,10 @@
         <v>1.26</v>
       </c>
       <c r="X356" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y356" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="357" spans="1:25" x14ac:dyDescent="0.2">
@@ -28006,10 +28006,10 @@
         <v>1.26</v>
       </c>
       <c r="X357" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y357" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="358" spans="1:25" x14ac:dyDescent="0.2">
@@ -28083,10 +28083,10 @@
         <v>1.26</v>
       </c>
       <c r="X358" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y358" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="359" spans="1:25" x14ac:dyDescent="0.2">
@@ -28160,10 +28160,10 @@
         <v>1.26</v>
       </c>
       <c r="X359" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y359" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="360" spans="1:25" x14ac:dyDescent="0.2">
@@ -28237,10 +28237,10 @@
         <v>1.26</v>
       </c>
       <c r="X360" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y360" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="361" spans="1:25" x14ac:dyDescent="0.2">
@@ -28314,10 +28314,10 @@
         <v>1.26</v>
       </c>
       <c r="X361" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y361" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="362" spans="1:25" x14ac:dyDescent="0.2">
@@ -28391,10 +28391,10 @@
         <v>1.26</v>
       </c>
       <c r="X362" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y362" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="363" spans="1:25" x14ac:dyDescent="0.2">
@@ -28468,10 +28468,10 @@
         <v>1.26</v>
       </c>
       <c r="X363" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y363" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="364" spans="1:25" x14ac:dyDescent="0.2">
@@ -28545,10 +28545,10 @@
         <v>1.26</v>
       </c>
       <c r="X364" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y364" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="365" spans="1:25" x14ac:dyDescent="0.2">
@@ -28622,10 +28622,10 @@
         <v>1.26</v>
       </c>
       <c r="X365" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y365" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="366" spans="1:25" x14ac:dyDescent="0.2">
@@ -28699,10 +28699,10 @@
         <v>1.26</v>
       </c>
       <c r="X366" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y366" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="367" spans="1:25" x14ac:dyDescent="0.2">
@@ -28776,10 +28776,10 @@
         <v>1.26</v>
       </c>
       <c r="X367" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y367" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="368" spans="1:25" x14ac:dyDescent="0.2">
@@ -28853,10 +28853,10 @@
         <v>1.26</v>
       </c>
       <c r="X368" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y368" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="369" spans="1:25" x14ac:dyDescent="0.2">
@@ -28930,10 +28930,10 @@
         <v>1.26</v>
       </c>
       <c r="X369" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y369" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="370" spans="1:25" x14ac:dyDescent="0.2">
@@ -29007,10 +29007,10 @@
         <v>1.26</v>
       </c>
       <c r="X370" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y370" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="371" spans="1:25" x14ac:dyDescent="0.2">
@@ -29084,10 +29084,10 @@
         <v>1.26</v>
       </c>
       <c r="X371" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y371" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="372" spans="1:25" x14ac:dyDescent="0.2">
@@ -29161,10 +29161,10 @@
         <v>1.26</v>
       </c>
       <c r="X372" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y372" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="373" spans="1:25" x14ac:dyDescent="0.2">
@@ -29238,10 +29238,10 @@
         <v>1.26</v>
       </c>
       <c r="X373" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y373" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="374" spans="1:25" x14ac:dyDescent="0.2">
@@ -29315,10 +29315,10 @@
         <v>1.26</v>
       </c>
       <c r="X374" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y374" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="375" spans="1:25" x14ac:dyDescent="0.2">
@@ -29392,10 +29392,10 @@
         <v>1.26</v>
       </c>
       <c r="X375" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y375" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="376" spans="1:25" x14ac:dyDescent="0.2">
@@ -29469,10 +29469,10 @@
         <v>1.26</v>
       </c>
       <c r="X376" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y376" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="377" spans="1:25" x14ac:dyDescent="0.2">
@@ -29546,10 +29546,10 @@
         <v>1.26</v>
       </c>
       <c r="X377" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y377" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="378" spans="1:25" x14ac:dyDescent="0.2">
@@ -29623,10 +29623,10 @@
         <v>1.26</v>
       </c>
       <c r="X378" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y378" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="379" spans="1:25" x14ac:dyDescent="0.2">
@@ -29700,10 +29700,10 @@
         <v>1.26</v>
       </c>
       <c r="X379" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y379" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="380" spans="1:25" x14ac:dyDescent="0.2">
@@ -29777,10 +29777,10 @@
         <v>1.26</v>
       </c>
       <c r="X380" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y380" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="381" spans="1:25" x14ac:dyDescent="0.2">
@@ -29854,10 +29854,10 @@
         <v>1.26</v>
       </c>
       <c r="X381" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y381" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="382" spans="1:25" x14ac:dyDescent="0.2">
@@ -29931,10 +29931,10 @@
         <v>1.26</v>
       </c>
       <c r="X382" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y382" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="383" spans="1:25" x14ac:dyDescent="0.2">
@@ -30008,10 +30008,10 @@
         <v>1.26</v>
       </c>
       <c r="X383" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y383" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="384" spans="1:25" x14ac:dyDescent="0.2">
@@ -30085,10 +30085,10 @@
         <v>1.26</v>
       </c>
       <c r="X384" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y384" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="385" spans="1:25" x14ac:dyDescent="0.2">
@@ -30162,10 +30162,10 @@
         <v>1.26</v>
       </c>
       <c r="X385" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y385" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="386" spans="1:25" x14ac:dyDescent="0.2">
@@ -30239,10 +30239,10 @@
         <v>1.26</v>
       </c>
       <c r="X386" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y386" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="387" spans="1:25" x14ac:dyDescent="0.2">
@@ -30316,10 +30316,10 @@
         <v>1.26</v>
       </c>
       <c r="X387" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y387" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="388" spans="1:25" x14ac:dyDescent="0.2">
@@ -30393,10 +30393,10 @@
         <v>1.26</v>
       </c>
       <c r="X388" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y388" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="389" spans="1:25" x14ac:dyDescent="0.2">
@@ -30470,10 +30470,10 @@
         <v>1.26</v>
       </c>
       <c r="X389" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y389" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="390" spans="1:25" x14ac:dyDescent="0.2">
@@ -30547,10 +30547,10 @@
         <v>1.26</v>
       </c>
       <c r="X390" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y390" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="391" spans="1:25" x14ac:dyDescent="0.2">
@@ -30624,10 +30624,10 @@
         <v>1.26</v>
       </c>
       <c r="X391" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y391" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="392" spans="1:25" x14ac:dyDescent="0.2">
@@ -30701,10 +30701,10 @@
         <v>1.26</v>
       </c>
       <c r="X392" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y392" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="393" spans="1:25" x14ac:dyDescent="0.2">
@@ -30778,10 +30778,10 @@
         <v>1.26</v>
       </c>
       <c r="X393" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y393" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="394" spans="1:25" x14ac:dyDescent="0.2">
@@ -30855,10 +30855,10 @@
         <v>1.26</v>
       </c>
       <c r="X394" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y394" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="395" spans="1:25" x14ac:dyDescent="0.2">
@@ -30932,10 +30932,10 @@
         <v>1.26</v>
       </c>
       <c r="X395" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y395" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="396" spans="1:25" x14ac:dyDescent="0.2">
@@ -31009,10 +31009,10 @@
         <v>1.26</v>
       </c>
       <c r="X396" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y396" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="397" spans="1:25" x14ac:dyDescent="0.2">
@@ -31086,10 +31086,10 @@
         <v>1.26</v>
       </c>
       <c r="X397" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y397" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="398" spans="1:25" x14ac:dyDescent="0.2">
@@ -31163,10 +31163,10 @@
         <v>1.26</v>
       </c>
       <c r="X398" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y398" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="399" spans="1:25" x14ac:dyDescent="0.2">
@@ -31240,10 +31240,10 @@
         <v>1.26</v>
       </c>
       <c r="X399" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y399" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="400" spans="1:25" x14ac:dyDescent="0.2">
@@ -31317,10 +31317,10 @@
         <v>1.26</v>
       </c>
       <c r="X400" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y400" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="401" spans="1:25" x14ac:dyDescent="0.2">
@@ -31394,10 +31394,10 @@
         <v>1.26</v>
       </c>
       <c r="X401" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y401" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="402" spans="1:25" x14ac:dyDescent="0.2">
@@ -31471,10 +31471,10 @@
         <v>1.26</v>
       </c>
       <c r="X402" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y402" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="403" spans="1:25" x14ac:dyDescent="0.2">
@@ -31548,10 +31548,10 @@
         <v>1.26</v>
       </c>
       <c r="X403" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y403" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="404" spans="1:25" x14ac:dyDescent="0.2">
@@ -31625,10 +31625,10 @@
         <v>1.26</v>
       </c>
       <c r="X404" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y404" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="405" spans="1:25" x14ac:dyDescent="0.2">
@@ -31702,10 +31702,10 @@
         <v>1.26</v>
       </c>
       <c r="X405" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y405" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="406" spans="1:25" x14ac:dyDescent="0.2">
@@ -31779,10 +31779,10 @@
         <v>1.26</v>
       </c>
       <c r="X406" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y406" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="407" spans="1:25" x14ac:dyDescent="0.2">
@@ -31856,10 +31856,10 @@
         <v>1.26</v>
       </c>
       <c r="X407" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y407" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="408" spans="1:25" x14ac:dyDescent="0.2">
@@ -31933,10 +31933,10 @@
         <v>1.26</v>
       </c>
       <c r="X408" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y408" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="409" spans="1:25" x14ac:dyDescent="0.2">
@@ -32010,10 +32010,10 @@
         <v>1.26</v>
       </c>
       <c r="X409" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y409" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="410" spans="1:25" x14ac:dyDescent="0.2">
@@ -32087,10 +32087,10 @@
         <v>1.26</v>
       </c>
       <c r="X410" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y410" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="411" spans="1:25" x14ac:dyDescent="0.2">
@@ -32164,10 +32164,10 @@
         <v>1.26</v>
       </c>
       <c r="X411" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y411" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="412" spans="1:25" x14ac:dyDescent="0.2">
@@ -32241,10 +32241,10 @@
         <v>1.26</v>
       </c>
       <c r="X412" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y412" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="413" spans="1:25" x14ac:dyDescent="0.2">
@@ -32318,10 +32318,10 @@
         <v>1.26</v>
       </c>
       <c r="X413" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y413" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="414" spans="1:25" x14ac:dyDescent="0.2">
@@ -32395,10 +32395,10 @@
         <v>1.26</v>
       </c>
       <c r="X414" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y414" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="415" spans="1:25" x14ac:dyDescent="0.2">
@@ -32472,10 +32472,10 @@
         <v>1.26</v>
       </c>
       <c r="X415" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y415" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="416" spans="1:25" x14ac:dyDescent="0.2">
@@ -32549,10 +32549,10 @@
         <v>1.26</v>
       </c>
       <c r="X416" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y416" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="417" spans="1:25" x14ac:dyDescent="0.2">
@@ -32626,10 +32626,10 @@
         <v>1.26</v>
       </c>
       <c r="X417" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y417" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="418" spans="1:25" x14ac:dyDescent="0.2">
@@ -32703,10 +32703,10 @@
         <v>1.26</v>
       </c>
       <c r="X418" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y418" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="419" spans="1:25" x14ac:dyDescent="0.2">
@@ -32780,10 +32780,10 @@
         <v>1.26</v>
       </c>
       <c r="X419" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y419" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="420" spans="1:25" x14ac:dyDescent="0.2">
@@ -32857,10 +32857,10 @@
         <v>1.26</v>
       </c>
       <c r="X420" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y420" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="421" spans="1:25" x14ac:dyDescent="0.2">
@@ -32934,10 +32934,10 @@
         <v>1.26</v>
       </c>
       <c r="X421" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y421" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="422" spans="1:25" x14ac:dyDescent="0.2">
@@ -33011,10 +33011,10 @@
         <v>1.26</v>
       </c>
       <c r="X422" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y422" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="423" spans="1:25" x14ac:dyDescent="0.2">
@@ -33088,10 +33088,10 @@
         <v>1.26</v>
       </c>
       <c r="X423" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y423" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="424" spans="1:25" x14ac:dyDescent="0.2">
@@ -33165,10 +33165,10 @@
         <v>1.26</v>
       </c>
       <c r="X424" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y424" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="425" spans="1:25" x14ac:dyDescent="0.2">
@@ -33242,10 +33242,10 @@
         <v>1.26</v>
       </c>
       <c r="X425" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y425" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="426" spans="1:25" x14ac:dyDescent="0.2">
@@ -33319,10 +33319,10 @@
         <v>1.26</v>
       </c>
       <c r="X426" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y426" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="427" spans="1:25" x14ac:dyDescent="0.2">
@@ -33396,10 +33396,10 @@
         <v>1.26</v>
       </c>
       <c r="X427" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y427" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="428" spans="1:25" x14ac:dyDescent="0.2">
@@ -33473,10 +33473,10 @@
         <v>1.26</v>
       </c>
       <c r="X428" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y428" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="429" spans="1:25" x14ac:dyDescent="0.2">
@@ -33550,10 +33550,10 @@
         <v>1.26</v>
       </c>
       <c r="X429" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y429" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="430" spans="1:25" x14ac:dyDescent="0.2">
@@ -33627,10 +33627,10 @@
         <v>1.26</v>
       </c>
       <c r="X430" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y430" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="431" spans="1:25" x14ac:dyDescent="0.2">
@@ -33704,10 +33704,10 @@
         <v>1.26</v>
       </c>
       <c r="X431" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y431" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="432" spans="1:25" x14ac:dyDescent="0.2">
@@ -33781,10 +33781,10 @@
         <v>1.26</v>
       </c>
       <c r="X432" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y432" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="433" spans="1:25" x14ac:dyDescent="0.2">
@@ -33858,10 +33858,10 @@
         <v>1.26</v>
       </c>
       <c r="X433" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y433" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="434" spans="1:25" x14ac:dyDescent="0.2">
@@ -33935,10 +33935,10 @@
         <v>1.26</v>
       </c>
       <c r="X434" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y434" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="435" spans="1:25" x14ac:dyDescent="0.2">
@@ -34012,10 +34012,10 @@
         <v>1.26</v>
       </c>
       <c r="X435" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y435" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="436" spans="1:25" x14ac:dyDescent="0.2">
@@ -34089,10 +34089,10 @@
         <v>1.26</v>
       </c>
       <c r="X436" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y436" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="437" spans="1:25" x14ac:dyDescent="0.2">
@@ -34166,10 +34166,10 @@
         <v>1.26</v>
       </c>
       <c r="X437" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y437" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="438" spans="1:25" x14ac:dyDescent="0.2">
@@ -34243,10 +34243,10 @@
         <v>1.26</v>
       </c>
       <c r="X438" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y438" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="439" spans="1:25" x14ac:dyDescent="0.2">
@@ -34320,10 +34320,10 @@
         <v>1.26</v>
       </c>
       <c r="X439" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y439" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="440" spans="1:25" x14ac:dyDescent="0.2">
@@ -34397,10 +34397,10 @@
         <v>1.26</v>
       </c>
       <c r="X440" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y440" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="441" spans="1:25" x14ac:dyDescent="0.2">
@@ -34474,10 +34474,10 @@
         <v>1.26</v>
       </c>
       <c r="X441" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y441" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="442" spans="1:25" x14ac:dyDescent="0.2">
@@ -34551,10 +34551,10 @@
         <v>1.26</v>
       </c>
       <c r="X442" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y442" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="443" spans="1:25" x14ac:dyDescent="0.2">
@@ -34628,10 +34628,10 @@
         <v>1.26</v>
       </c>
       <c r="X443" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y443" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="444" spans="1:25" x14ac:dyDescent="0.2">
@@ -34705,10 +34705,10 @@
         <v>1.26</v>
       </c>
       <c r="X444" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y444" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="445" spans="1:25" x14ac:dyDescent="0.2">
@@ -34782,10 +34782,10 @@
         <v>1.26</v>
       </c>
       <c r="X445" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y445" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="446" spans="1:25" x14ac:dyDescent="0.2">
@@ -34859,10 +34859,10 @@
         <v>1.26</v>
       </c>
       <c r="X446" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y446" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="447" spans="1:25" x14ac:dyDescent="0.2">
@@ -34936,10 +34936,10 @@
         <v>1.26</v>
       </c>
       <c r="X447" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y447" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="448" spans="1:25" x14ac:dyDescent="0.2">
@@ -35013,10 +35013,10 @@
         <v>1.26</v>
       </c>
       <c r="X448" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y448" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="449" spans="1:25" x14ac:dyDescent="0.2">
@@ -35090,10 +35090,10 @@
         <v>1.26</v>
       </c>
       <c r="X449" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y449" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="450" spans="1:25" x14ac:dyDescent="0.2">
@@ -35167,10 +35167,10 @@
         <v>1.26</v>
       </c>
       <c r="X450" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y450" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="451" spans="1:25" x14ac:dyDescent="0.2">
@@ -35244,10 +35244,10 @@
         <v>1.26</v>
       </c>
       <c r="X451" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y451" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="452" spans="1:25" x14ac:dyDescent="0.2">
@@ -35321,10 +35321,10 @@
         <v>1.26</v>
       </c>
       <c r="X452" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y452" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="453" spans="1:25" x14ac:dyDescent="0.2">
@@ -35398,10 +35398,10 @@
         <v>1.26</v>
       </c>
       <c r="X453" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y453" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="454" spans="1:25" x14ac:dyDescent="0.2">
@@ -35475,10 +35475,10 @@
         <v>1.26</v>
       </c>
       <c r="X454" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y454" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="455" spans="1:25" x14ac:dyDescent="0.2">
@@ -35552,10 +35552,10 @@
         <v>1.26</v>
       </c>
       <c r="X455" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y455" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="456" spans="1:25" x14ac:dyDescent="0.2">
@@ -35629,10 +35629,10 @@
         <v>1.26</v>
       </c>
       <c r="X456" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y456" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="457" spans="1:25" x14ac:dyDescent="0.2">
@@ -35706,10 +35706,10 @@
         <v>1.26</v>
       </c>
       <c r="X457" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y457" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="458" spans="1:25" x14ac:dyDescent="0.2">
@@ -35783,10 +35783,10 @@
         <v>1.26</v>
       </c>
       <c r="X458" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y458" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="459" spans="1:25" x14ac:dyDescent="0.2">
@@ -35860,10 +35860,10 @@
         <v>1.26</v>
       </c>
       <c r="X459" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y459" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="460" spans="1:25" x14ac:dyDescent="0.2">
@@ -35937,10 +35937,10 @@
         <v>1.26</v>
       </c>
       <c r="X460" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y460" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="461" spans="1:25" x14ac:dyDescent="0.2">
@@ -36014,10 +36014,10 @@
         <v>1.26</v>
       </c>
       <c r="X461" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y461" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="462" spans="1:25" x14ac:dyDescent="0.2">
@@ -36091,10 +36091,10 @@
         <v>1.26</v>
       </c>
       <c r="X462" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y462" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="463" spans="1:25" x14ac:dyDescent="0.2">
@@ -36168,10 +36168,10 @@
         <v>1.26</v>
       </c>
       <c r="X463" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y463" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="464" spans="1:25" x14ac:dyDescent="0.2">
@@ -36245,10 +36245,10 @@
         <v>1.26</v>
       </c>
       <c r="X464" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y464" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="465" spans="1:25" x14ac:dyDescent="0.2">
@@ -36322,10 +36322,10 @@
         <v>1.26</v>
       </c>
       <c r="X465" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y465" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="466" spans="1:25" x14ac:dyDescent="0.2">
@@ -36399,10 +36399,10 @@
         <v>1.26</v>
       </c>
       <c r="X466" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y466" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="467" spans="1:25" x14ac:dyDescent="0.2">
@@ -36476,10 +36476,10 @@
         <v>1.26</v>
       </c>
       <c r="X467" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y467" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="468" spans="1:25" x14ac:dyDescent="0.2">
@@ -36553,10 +36553,10 @@
         <v>1.26</v>
       </c>
       <c r="X468" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y468" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="469" spans="1:25" x14ac:dyDescent="0.2">
@@ -36630,10 +36630,10 @@
         <v>1.26</v>
       </c>
       <c r="X469" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y469" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="470" spans="1:25" x14ac:dyDescent="0.2">
@@ -36707,10 +36707,10 @@
         <v>1.26</v>
       </c>
       <c r="X470" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y470" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="471" spans="1:25" x14ac:dyDescent="0.2">
@@ -36784,10 +36784,10 @@
         <v>1.26</v>
       </c>
       <c r="X471" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y471" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="472" spans="1:25" x14ac:dyDescent="0.2">
@@ -36861,10 +36861,10 @@
         <v>1.26</v>
       </c>
       <c r="X472" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y472" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="473" spans="1:25" x14ac:dyDescent="0.2">
@@ -36938,10 +36938,10 @@
         <v>1.26</v>
       </c>
       <c r="X473" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y473" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="474" spans="1:25" x14ac:dyDescent="0.2">
@@ -37015,10 +37015,10 @@
         <v>1.26</v>
       </c>
       <c r="X474" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y474" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="475" spans="1:25" x14ac:dyDescent="0.2">
@@ -37092,10 +37092,10 @@
         <v>1.26</v>
       </c>
       <c r="X475" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y475" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="476" spans="1:25" x14ac:dyDescent="0.2">
@@ -37169,10 +37169,10 @@
         <v>1.26</v>
       </c>
       <c r="X476" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y476" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="477" spans="1:25" x14ac:dyDescent="0.2">
@@ -37246,10 +37246,10 @@
         <v>1.26</v>
       </c>
       <c r="X477" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y477" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="478" spans="1:25" x14ac:dyDescent="0.2">
@@ -37323,10 +37323,10 @@
         <v>1.26</v>
       </c>
       <c r="X478" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y478" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="479" spans="1:25" x14ac:dyDescent="0.2">
@@ -37400,10 +37400,10 @@
         <v>1.26</v>
       </c>
       <c r="X479" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y479" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="480" spans="1:25" x14ac:dyDescent="0.2">
@@ -37477,10 +37477,10 @@
         <v>1.26</v>
       </c>
       <c r="X480" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y480" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="481" spans="1:25" x14ac:dyDescent="0.2">
@@ -37554,10 +37554,10 @@
         <v>1.26</v>
       </c>
       <c r="X481" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y481" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="482" spans="1:25" x14ac:dyDescent="0.2">
@@ -37631,10 +37631,10 @@
         <v>1.26</v>
       </c>
       <c r="X482" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y482" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="483" spans="1:25" x14ac:dyDescent="0.2">
@@ -37708,10 +37708,10 @@
         <v>1.26</v>
       </c>
       <c r="X483" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y483" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="484" spans="1:25" x14ac:dyDescent="0.2">
@@ -37785,10 +37785,10 @@
         <v>1.26</v>
       </c>
       <c r="X484" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y484" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="485" spans="1:25" x14ac:dyDescent="0.2">
@@ -37862,10 +37862,10 @@
         <v>1.26</v>
       </c>
       <c r="X485" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y485" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="486" spans="1:25" x14ac:dyDescent="0.2">
@@ -37939,10 +37939,10 @@
         <v>1.26</v>
       </c>
       <c r="X486" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y486" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="487" spans="1:25" x14ac:dyDescent="0.2">
@@ -38016,10 +38016,10 @@
         <v>1.26</v>
       </c>
       <c r="X487" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y487" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="488" spans="1:25" x14ac:dyDescent="0.2">
@@ -38093,10 +38093,10 @@
         <v>1.26</v>
       </c>
       <c r="X488" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y488" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="489" spans="1:25" x14ac:dyDescent="0.2">
@@ -38170,10 +38170,10 @@
         <v>1.26</v>
       </c>
       <c r="X489" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y489" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="490" spans="1:25" x14ac:dyDescent="0.2">
@@ -38247,10 +38247,10 @@
         <v>1.26</v>
       </c>
       <c r="X490" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y490" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="491" spans="1:25" x14ac:dyDescent="0.2">
@@ -38324,10 +38324,10 @@
         <v>1.26</v>
       </c>
       <c r="X491" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y491" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="492" spans="1:25" x14ac:dyDescent="0.2">
@@ -38401,10 +38401,10 @@
         <v>1.26</v>
       </c>
       <c r="X492" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y492" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="493" spans="1:25" x14ac:dyDescent="0.2">
@@ -38478,10 +38478,10 @@
         <v>1.26</v>
       </c>
       <c r="X493" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y493" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="494" spans="1:25" x14ac:dyDescent="0.2">
@@ -38555,10 +38555,10 @@
         <v>1.26</v>
       </c>
       <c r="X494" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y494" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="495" spans="1:25" x14ac:dyDescent="0.2">
@@ -38632,10 +38632,10 @@
         <v>1.26</v>
       </c>
       <c r="X495" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y495" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="496" spans="1:25" x14ac:dyDescent="0.2">
@@ -38709,10 +38709,10 @@
         <v>1.26</v>
       </c>
       <c r="X496" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y496" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="497" spans="1:25" x14ac:dyDescent="0.2">
@@ -38786,10 +38786,10 @@
         <v>1.26</v>
       </c>
       <c r="X497" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y497" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="498" spans="1:25" x14ac:dyDescent="0.2">
@@ -38863,10 +38863,10 @@
         <v>1.26</v>
       </c>
       <c r="X498" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y498" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="499" spans="1:25" x14ac:dyDescent="0.2">
@@ -38940,10 +38940,10 @@
         <v>1.26</v>
       </c>
       <c r="X499" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y499" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="500" spans="1:25" x14ac:dyDescent="0.2">
@@ -39017,10 +39017,10 @@
         <v>1.26</v>
       </c>
       <c r="X500" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y500" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="501" spans="1:25" x14ac:dyDescent="0.2">
@@ -39094,10 +39094,10 @@
         <v>1.26</v>
       </c>
       <c r="X501" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y501" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="502" spans="1:25" x14ac:dyDescent="0.2">
@@ -39171,10 +39171,10 @@
         <v>1.26</v>
       </c>
       <c r="X502" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y502" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="503" spans="1:25" x14ac:dyDescent="0.2">
@@ -39248,10 +39248,10 @@
         <v>1.26</v>
       </c>
       <c r="X503" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y503" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="504" spans="1:25" x14ac:dyDescent="0.2">
@@ -39325,10 +39325,10 @@
         <v>1.26</v>
       </c>
       <c r="X504" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y504" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="505" spans="1:25" x14ac:dyDescent="0.2">
@@ -39402,10 +39402,10 @@
         <v>1.26</v>
       </c>
       <c r="X505" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y505" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="506" spans="1:25" x14ac:dyDescent="0.2">
@@ -39479,10 +39479,10 @@
         <v>1.26</v>
       </c>
       <c r="X506" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y506" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="507" spans="1:25" x14ac:dyDescent="0.2">
@@ -39556,10 +39556,10 @@
         <v>1.26</v>
       </c>
       <c r="X507" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y507" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="508" spans="1:25" x14ac:dyDescent="0.2">
@@ -39633,10 +39633,10 @@
         <v>1.26</v>
       </c>
       <c r="X508" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y508" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="509" spans="1:25" x14ac:dyDescent="0.2">
@@ -39710,10 +39710,10 @@
         <v>1.26</v>
       </c>
       <c r="X509" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y509" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="510" spans="1:25" x14ac:dyDescent="0.2">
@@ -39787,10 +39787,10 @@
         <v>1.26</v>
       </c>
       <c r="X510" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y510" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="511" spans="1:25" x14ac:dyDescent="0.2">
@@ -39864,10 +39864,10 @@
         <v>1.26</v>
       </c>
       <c r="X511" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y511" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="512" spans="1:25" x14ac:dyDescent="0.2">
@@ -39941,10 +39941,10 @@
         <v>1.26</v>
       </c>
       <c r="X512" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y512" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="513" spans="1:25" x14ac:dyDescent="0.2">
@@ -40018,10 +40018,10 @@
         <v>1.26</v>
       </c>
       <c r="X513" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y513" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="514" spans="1:25" x14ac:dyDescent="0.2">
@@ -40095,10 +40095,10 @@
         <v>1.26</v>
       </c>
       <c r="X514" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y514" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="515" spans="1:25" x14ac:dyDescent="0.2">
@@ -40172,10 +40172,10 @@
         <v>1.26</v>
       </c>
       <c r="X515" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y515" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="516" spans="1:25" x14ac:dyDescent="0.2">
@@ -40249,10 +40249,10 @@
         <v>1.26</v>
       </c>
       <c r="X516" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y516" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="517" spans="1:25" x14ac:dyDescent="0.2">
@@ -40326,10 +40326,10 @@
         <v>1.26</v>
       </c>
       <c r="X517" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y517" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="518" spans="1:25" x14ac:dyDescent="0.2">
@@ -40403,10 +40403,10 @@
         <v>1.26</v>
       </c>
       <c r="X518" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y518" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="519" spans="1:25" x14ac:dyDescent="0.2">
@@ -40480,10 +40480,10 @@
         <v>1.26</v>
       </c>
       <c r="X519" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y519" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="520" spans="1:25" x14ac:dyDescent="0.2">
@@ -40557,10 +40557,10 @@
         <v>1.26</v>
       </c>
       <c r="X520" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y520" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="521" spans="1:25" x14ac:dyDescent="0.2">
@@ -40634,10 +40634,10 @@
         <v>1.26</v>
       </c>
       <c r="X521" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y521" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="522" spans="1:25" x14ac:dyDescent="0.2">
@@ -40711,10 +40711,10 @@
         <v>1.26</v>
       </c>
       <c r="X522" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y522" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="523" spans="1:25" x14ac:dyDescent="0.2">
@@ -40788,10 +40788,10 @@
         <v>1.26</v>
       </c>
       <c r="X523" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y523" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="524" spans="1:25" x14ac:dyDescent="0.2">
@@ -40865,10 +40865,10 @@
         <v>1.26</v>
       </c>
       <c r="X524" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y524" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="525" spans="1:25" x14ac:dyDescent="0.2">
@@ -40942,10 +40942,10 @@
         <v>1.26</v>
       </c>
       <c r="X525" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y525" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="526" spans="1:25" x14ac:dyDescent="0.2">
@@ -41019,10 +41019,10 @@
         <v>1.26</v>
       </c>
       <c r="X526" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y526" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="527" spans="1:25" x14ac:dyDescent="0.2">
@@ -41096,10 +41096,10 @@
         <v>1.26</v>
       </c>
       <c r="X527" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y527" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="528" spans="1:25" x14ac:dyDescent="0.2">
@@ -41173,10 +41173,10 @@
         <v>1.26</v>
       </c>
       <c r="X528" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y528" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="529" spans="1:25" x14ac:dyDescent="0.2">
@@ -41250,10 +41250,10 @@
         <v>1.26</v>
       </c>
       <c r="X529" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y529" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="530" spans="1:25" x14ac:dyDescent="0.2">
@@ -41327,10 +41327,10 @@
         <v>1.26</v>
       </c>
       <c r="X530" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y530" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="531" spans="1:25" x14ac:dyDescent="0.2">
@@ -41404,10 +41404,10 @@
         <v>1.26</v>
       </c>
       <c r="X531" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y531" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="532" spans="1:25" x14ac:dyDescent="0.2">
@@ -41481,10 +41481,10 @@
         <v>1.26</v>
       </c>
       <c r="X532" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y532" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="533" spans="1:25" x14ac:dyDescent="0.2">
@@ -41558,10 +41558,10 @@
         <v>1.26</v>
       </c>
       <c r="X533" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y533" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="534" spans="1:25" x14ac:dyDescent="0.2">
@@ -41635,10 +41635,10 @@
         <v>1.26</v>
       </c>
       <c r="X534" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y534" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="535" spans="1:25" x14ac:dyDescent="0.2">
@@ -41712,10 +41712,10 @@
         <v>1.26</v>
       </c>
       <c r="X535" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y535" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="536" spans="1:25" x14ac:dyDescent="0.2">
@@ -41789,10 +41789,10 @@
         <v>1.26</v>
       </c>
       <c r="X536" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y536" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="537" spans="1:25" x14ac:dyDescent="0.2">
@@ -41866,10 +41866,10 @@
         <v>1.26</v>
       </c>
       <c r="X537" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y537" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="538" spans="1:25" x14ac:dyDescent="0.2">
@@ -41943,10 +41943,10 @@
         <v>1.26</v>
       </c>
       <c r="X538" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y538" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="539" spans="1:25" x14ac:dyDescent="0.2">
@@ -42020,10 +42020,10 @@
         <v>1.26</v>
       </c>
       <c r="X539" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y539" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="540" spans="1:25" x14ac:dyDescent="0.2">
@@ -42097,10 +42097,10 @@
         <v>1.26</v>
       </c>
       <c r="X540" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y540" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="541" spans="1:25" x14ac:dyDescent="0.2">
@@ -42174,10 +42174,10 @@
         <v>1.26</v>
       </c>
       <c r="X541" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y541" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="542" spans="1:25" x14ac:dyDescent="0.2">
@@ -42251,10 +42251,10 @@
         <v>1.26</v>
       </c>
       <c r="X542" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y542" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="543" spans="1:25" x14ac:dyDescent="0.2">
@@ -42328,10 +42328,10 @@
         <v>1.26</v>
       </c>
       <c r="X543" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y543" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="544" spans="1:25" x14ac:dyDescent="0.2">
@@ -42405,10 +42405,10 @@
         <v>1.26</v>
       </c>
       <c r="X544" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y544" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="545" spans="1:25" x14ac:dyDescent="0.2">
@@ -42482,10 +42482,10 @@
         <v>1.26</v>
       </c>
       <c r="X545" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y545" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="546" spans="1:25" x14ac:dyDescent="0.2">
@@ -42559,10 +42559,10 @@
         <v>1.26</v>
       </c>
       <c r="X546" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y546" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="547" spans="1:25" x14ac:dyDescent="0.2">
@@ -42636,10 +42636,10 @@
         <v>1.26</v>
       </c>
       <c r="X547" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y547" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="548" spans="1:25" x14ac:dyDescent="0.2">
@@ -42713,10 +42713,10 @@
         <v>1.26</v>
       </c>
       <c r="X548" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y548" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="549" spans="1:25" x14ac:dyDescent="0.2">
@@ -42790,10 +42790,10 @@
         <v>1.26</v>
       </c>
       <c r="X549" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y549" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="550" spans="1:25" x14ac:dyDescent="0.2">
@@ -42867,10 +42867,10 @@
         <v>1.26</v>
       </c>
       <c r="X550" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y550" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="551" spans="1:25" x14ac:dyDescent="0.2">
@@ -42944,10 +42944,10 @@
         <v>1.26</v>
       </c>
       <c r="X551" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y551" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="552" spans="1:25" x14ac:dyDescent="0.2">
@@ -43021,10 +43021,10 @@
         <v>1.26</v>
       </c>
       <c r="X552" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y552" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="553" spans="1:25" x14ac:dyDescent="0.2">
@@ -43098,10 +43098,10 @@
         <v>1.26</v>
       </c>
       <c r="X553" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y553" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="554" spans="1:25" x14ac:dyDescent="0.2">
@@ -43175,10 +43175,10 @@
         <v>1.26</v>
       </c>
       <c r="X554" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y554" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="555" spans="1:25" x14ac:dyDescent="0.2">
@@ -43252,10 +43252,10 @@
         <v>1.26</v>
       </c>
       <c r="X555" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y555" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="556" spans="1:25" x14ac:dyDescent="0.2">
@@ -43329,10 +43329,10 @@
         <v>1.26</v>
       </c>
       <c r="X556" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y556" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="557" spans="1:25" x14ac:dyDescent="0.2">
@@ -43406,10 +43406,10 @@
         <v>1.26</v>
       </c>
       <c r="X557" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y557" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="558" spans="1:25" x14ac:dyDescent="0.2">
@@ -43483,10 +43483,10 @@
         <v>1.26</v>
       </c>
       <c r="X558" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y558" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="559" spans="1:25" x14ac:dyDescent="0.2">
@@ -43560,10 +43560,10 @@
         <v>1.26</v>
       </c>
       <c r="X559" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y559" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="560" spans="1:25" x14ac:dyDescent="0.2">
@@ -43637,10 +43637,10 @@
         <v>1.26</v>
       </c>
       <c r="X560" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y560" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="561" spans="1:25" x14ac:dyDescent="0.2">
@@ -43714,10 +43714,10 @@
         <v>1.26</v>
       </c>
       <c r="X561" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y561" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="562" spans="1:25" x14ac:dyDescent="0.2">
@@ -43791,10 +43791,10 @@
         <v>1.26</v>
       </c>
       <c r="X562" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y562" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="563" spans="1:25" x14ac:dyDescent="0.2">
@@ -43868,10 +43868,10 @@
         <v>1.26</v>
       </c>
       <c r="X563" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y563" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="564" spans="1:25" x14ac:dyDescent="0.2">
@@ -43945,10 +43945,10 @@
         <v>1.26</v>
       </c>
       <c r="X564" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y564" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="565" spans="1:25" x14ac:dyDescent="0.2">
@@ -44022,10 +44022,10 @@
         <v>1.26</v>
       </c>
       <c r="X565" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y565" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="566" spans="1:25" x14ac:dyDescent="0.2">
@@ -44099,10 +44099,10 @@
         <v>1.26</v>
       </c>
       <c r="X566" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y566" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="567" spans="1:25" x14ac:dyDescent="0.2">
@@ -44176,10 +44176,10 @@
         <v>1.26</v>
       </c>
       <c r="X567" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y567" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="568" spans="1:25" x14ac:dyDescent="0.2">
@@ -44253,10 +44253,10 @@
         <v>1.26</v>
       </c>
       <c r="X568" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y568" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="569" spans="1:25" x14ac:dyDescent="0.2">
@@ -44330,10 +44330,10 @@
         <v>1.26</v>
       </c>
       <c r="X569" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y569" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="570" spans="1:25" x14ac:dyDescent="0.2">
@@ -44407,10 +44407,10 @@
         <v>1.26</v>
       </c>
       <c r="X570" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y570" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="571" spans="1:25" x14ac:dyDescent="0.2">
@@ -44484,10 +44484,10 @@
         <v>1.26</v>
       </c>
       <c r="X571" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y571" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="572" spans="1:25" x14ac:dyDescent="0.2">
@@ -44561,10 +44561,10 @@
         <v>1.26</v>
       </c>
       <c r="X572" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y572" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="573" spans="1:25" x14ac:dyDescent="0.2">
@@ -44638,10 +44638,10 @@
         <v>1.26</v>
       </c>
       <c r="X573" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y573" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="574" spans="1:25" x14ac:dyDescent="0.2">
@@ -44715,10 +44715,10 @@
         <v>1.26</v>
       </c>
       <c r="X574" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y574" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="575" spans="1:25" x14ac:dyDescent="0.2">
@@ -44792,10 +44792,10 @@
         <v>1.26</v>
       </c>
       <c r="X575" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y575" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="576" spans="1:25" x14ac:dyDescent="0.2">
@@ -44869,10 +44869,10 @@
         <v>1.26</v>
       </c>
       <c r="X576" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y576" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="577" spans="1:25" x14ac:dyDescent="0.2">
@@ -44946,10 +44946,10 @@
         <v>1.26</v>
       </c>
       <c r="X577" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y577" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="578" spans="1:25" x14ac:dyDescent="0.2">
@@ -45023,10 +45023,10 @@
         <v>1.26</v>
       </c>
       <c r="X578" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y578" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="579" spans="1:25" x14ac:dyDescent="0.2">
@@ -45100,10 +45100,10 @@
         <v>1.26</v>
       </c>
       <c r="X579" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y579" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="580" spans="1:25" x14ac:dyDescent="0.2">
@@ -45177,10 +45177,10 @@
         <v>1.26</v>
       </c>
       <c r="X580" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y580" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="581" spans="1:25" x14ac:dyDescent="0.2">
@@ -45254,10 +45254,10 @@
         <v>1.26</v>
       </c>
       <c r="X581" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y581" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="582" spans="1:25" x14ac:dyDescent="0.2">
@@ -45331,10 +45331,10 @@
         <v>1.26</v>
       </c>
       <c r="X582" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y582" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="583" spans="1:25" x14ac:dyDescent="0.2">
@@ -45408,10 +45408,10 @@
         <v>1.26</v>
       </c>
       <c r="X583" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y583" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="584" spans="1:25" x14ac:dyDescent="0.2">
@@ -45485,10 +45485,10 @@
         <v>1.26</v>
       </c>
       <c r="X584" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y584" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="585" spans="1:25" x14ac:dyDescent="0.2">
@@ -45562,10 +45562,10 @@
         <v>1.26</v>
       </c>
       <c r="X585" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y585" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="586" spans="1:25" x14ac:dyDescent="0.2">
@@ -45639,10 +45639,10 @@
         <v>1.26</v>
       </c>
       <c r="X586" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y586" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="587" spans="1:25" x14ac:dyDescent="0.2">
@@ -45716,10 +45716,10 @@
         <v>1.26</v>
       </c>
       <c r="X587" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y587" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="588" spans="1:25" x14ac:dyDescent="0.2">
@@ -45793,10 +45793,10 @@
         <v>1.26</v>
       </c>
       <c r="X588" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y588" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="589" spans="1:25" x14ac:dyDescent="0.2">
@@ -45870,10 +45870,10 @@
         <v>1.26</v>
       </c>
       <c r="X589" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y589" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="590" spans="1:25" x14ac:dyDescent="0.2">
@@ -45947,10 +45947,10 @@
         <v>1.26</v>
       </c>
       <c r="X590" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y590" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="591" spans="1:25" x14ac:dyDescent="0.2">
@@ -46024,10 +46024,10 @@
         <v>1.26</v>
       </c>
       <c r="X591" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y591" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="592" spans="1:25" x14ac:dyDescent="0.2">
@@ -46101,10 +46101,10 @@
         <v>1.26</v>
       </c>
       <c r="X592" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y592" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="593" spans="1:25" x14ac:dyDescent="0.2">
@@ -46178,10 +46178,10 @@
         <v>1.26</v>
       </c>
       <c r="X593" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y593" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="594" spans="1:25" x14ac:dyDescent="0.2">
@@ -46255,10 +46255,10 @@
         <v>1.26</v>
       </c>
       <c r="X594" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y594" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="595" spans="1:25" x14ac:dyDescent="0.2">
@@ -46332,10 +46332,10 @@
         <v>1.26</v>
       </c>
       <c r="X595" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y595" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="596" spans="1:25" x14ac:dyDescent="0.2">
@@ -46409,10 +46409,10 @@
         <v>1.26</v>
       </c>
       <c r="X596" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y596" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="597" spans="1:25" x14ac:dyDescent="0.2">
@@ -46486,10 +46486,10 @@
         <v>1.26</v>
       </c>
       <c r="X597" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y597" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="598" spans="1:25" x14ac:dyDescent="0.2">
@@ -46563,10 +46563,10 @@
         <v>1.26</v>
       </c>
       <c r="X598" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y598" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="599" spans="1:25" x14ac:dyDescent="0.2">
@@ -46640,10 +46640,10 @@
         <v>1.26</v>
       </c>
       <c r="X599" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y599" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="600" spans="1:25" x14ac:dyDescent="0.2">
@@ -46717,10 +46717,10 @@
         <v>1.26</v>
       </c>
       <c r="X600" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y600" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="601" spans="1:25" x14ac:dyDescent="0.2">
@@ -46794,10 +46794,10 @@
         <v>1.26</v>
       </c>
       <c r="X601" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y601" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="602" spans="1:25" x14ac:dyDescent="0.2">
@@ -46871,10 +46871,10 @@
         <v>1.26</v>
       </c>
       <c r="X602" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y602" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="603" spans="1:25" x14ac:dyDescent="0.2">
@@ -46948,10 +46948,10 @@
         <v>1.26</v>
       </c>
       <c r="X603" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y603" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="604" spans="1:25" x14ac:dyDescent="0.2">
@@ -47025,10 +47025,10 @@
         <v>1.26</v>
       </c>
       <c r="X604" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y604" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="605" spans="1:25" x14ac:dyDescent="0.2">
@@ -47102,10 +47102,10 @@
         <v>1.26</v>
       </c>
       <c r="X605" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y605" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="606" spans="1:25" x14ac:dyDescent="0.2">
@@ -47179,10 +47179,10 @@
         <v>1.26</v>
       </c>
       <c r="X606" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y606" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="607" spans="1:25" x14ac:dyDescent="0.2">
@@ -47256,10 +47256,10 @@
         <v>1.26</v>
       </c>
       <c r="X607" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y607" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="608" spans="1:25" x14ac:dyDescent="0.2">
@@ -47333,10 +47333,10 @@
         <v>1.26</v>
       </c>
       <c r="X608" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y608" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="609" spans="1:25" x14ac:dyDescent="0.2">
@@ -47410,10 +47410,10 @@
         <v>1.26</v>
       </c>
       <c r="X609" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y609" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="610" spans="1:25" x14ac:dyDescent="0.2">
@@ -47487,10 +47487,10 @@
         <v>1.26</v>
       </c>
       <c r="X610" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y610" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="611" spans="1:25" x14ac:dyDescent="0.2">
@@ -47564,10 +47564,10 @@
         <v>1.26</v>
       </c>
       <c r="X611" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y611" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="612" spans="1:25" x14ac:dyDescent="0.2">
@@ -47641,10 +47641,10 @@
         <v>1.26</v>
       </c>
       <c r="X612" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y612" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="613" spans="1:25" x14ac:dyDescent="0.2">
@@ -47718,10 +47718,10 @@
         <v>1.26</v>
       </c>
       <c r="X613" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y613" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="614" spans="1:25" x14ac:dyDescent="0.2">
@@ -47795,10 +47795,10 @@
         <v>1.26</v>
       </c>
       <c r="X614" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y614" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="615" spans="1:25" x14ac:dyDescent="0.2">
@@ -47872,10 +47872,10 @@
         <v>1.26</v>
       </c>
       <c r="X615" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y615" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="616" spans="1:25" x14ac:dyDescent="0.2">
@@ -47949,10 +47949,10 @@
         <v>1.26</v>
       </c>
       <c r="X616" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y616" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="617" spans="1:25" x14ac:dyDescent="0.2">
@@ -48026,10 +48026,10 @@
         <v>1.26</v>
       </c>
       <c r="X617" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y617" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="618" spans="1:25" x14ac:dyDescent="0.2">
@@ -48103,10 +48103,10 @@
         <v>1.26</v>
       </c>
       <c r="X618" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y618" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="619" spans="1:25" x14ac:dyDescent="0.2">
@@ -48180,10 +48180,10 @@
         <v>1.26</v>
       </c>
       <c r="X619" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y619" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="620" spans="1:25" x14ac:dyDescent="0.2">
@@ -48257,10 +48257,10 @@
         <v>1.26</v>
       </c>
       <c r="X620" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y620" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="621" spans="1:25" x14ac:dyDescent="0.2">
@@ -48334,10 +48334,10 @@
         <v>1.26</v>
       </c>
       <c r="X621" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y621" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="622" spans="1:25" x14ac:dyDescent="0.2">
@@ -48411,10 +48411,10 @@
         <v>1.26</v>
       </c>
       <c r="X622" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y622" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="623" spans="1:25" x14ac:dyDescent="0.2">
@@ -48488,10 +48488,10 @@
         <v>1.26</v>
       </c>
       <c r="X623" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y623" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="624" spans="1:25" x14ac:dyDescent="0.2">
@@ -48565,10 +48565,10 @@
         <v>1.26</v>
       </c>
       <c r="X624" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y624" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="625" spans="1:25" x14ac:dyDescent="0.2">
@@ -48642,10 +48642,10 @@
         <v>1.26</v>
       </c>
       <c r="X625" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y625" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="626" spans="1:25" x14ac:dyDescent="0.2">
@@ -48719,10 +48719,10 @@
         <v>1.26</v>
       </c>
       <c r="X626" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y626" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="627" spans="1:25" x14ac:dyDescent="0.2">
@@ -48796,10 +48796,10 @@
         <v>1.26</v>
       </c>
       <c r="X627" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y627" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="628" spans="1:25" x14ac:dyDescent="0.2">
@@ -48873,10 +48873,10 @@
         <v>1.26</v>
       </c>
       <c r="X628" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y628" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="629" spans="1:25" x14ac:dyDescent="0.2">
@@ -48950,10 +48950,10 @@
         <v>1.26</v>
       </c>
       <c r="X629" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y629" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="630" spans="1:25" x14ac:dyDescent="0.2">
@@ -49027,10 +49027,10 @@
         <v>1.26</v>
       </c>
       <c r="X630" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y630" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="631" spans="1:25" x14ac:dyDescent="0.2">
@@ -49104,10 +49104,10 @@
         <v>1.26</v>
       </c>
       <c r="X631" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y631" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="632" spans="1:25" x14ac:dyDescent="0.2">
@@ -49181,10 +49181,10 @@
         <v>1.26</v>
       </c>
       <c r="X632" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y632" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="633" spans="1:25" x14ac:dyDescent="0.2">
@@ -49258,10 +49258,10 @@
         <v>1.26</v>
       </c>
       <c r="X633" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y633" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="634" spans="1:25" x14ac:dyDescent="0.2">
@@ -49335,10 +49335,10 @@
         <v>1.26</v>
       </c>
       <c r="X634" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y634" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="635" spans="1:25" x14ac:dyDescent="0.2">
@@ -49412,10 +49412,10 @@
         <v>1.26</v>
       </c>
       <c r="X635" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y635" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="636" spans="1:25" x14ac:dyDescent="0.2">
@@ -49489,10 +49489,10 @@
         <v>1.26</v>
       </c>
       <c r="X636" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y636" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="637" spans="1:25" x14ac:dyDescent="0.2">
@@ -49566,10 +49566,10 @@
         <v>1.26</v>
       </c>
       <c r="X637" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y637" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="638" spans="1:25" x14ac:dyDescent="0.2">
@@ -49643,10 +49643,10 @@
         <v>1.26</v>
       </c>
       <c r="X638" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y638" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="639" spans="1:25" x14ac:dyDescent="0.2">
@@ -49720,10 +49720,10 @@
         <v>1.26</v>
       </c>
       <c r="X639" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y639" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="640" spans="1:25" x14ac:dyDescent="0.2">
@@ -49797,10 +49797,10 @@
         <v>1.26</v>
       </c>
       <c r="X640" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y640" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="641" spans="1:25" x14ac:dyDescent="0.2">
@@ -49874,10 +49874,10 @@
         <v>1.26</v>
       </c>
       <c r="X641" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y641" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="642" spans="1:25" x14ac:dyDescent="0.2">
@@ -49951,10 +49951,10 @@
         <v>1.26</v>
       </c>
       <c r="X642" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y642" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="643" spans="1:25" x14ac:dyDescent="0.2">
@@ -50028,10 +50028,10 @@
         <v>1.26</v>
       </c>
       <c r="X643" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y643" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="644" spans="1:25" x14ac:dyDescent="0.2">
@@ -50105,10 +50105,10 @@
         <v>1.26</v>
       </c>
       <c r="X644" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y644" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="645" spans="1:25" x14ac:dyDescent="0.2">
@@ -50182,10 +50182,10 @@
         <v>1.26</v>
       </c>
       <c r="X645" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y645" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="646" spans="1:25" x14ac:dyDescent="0.2">
@@ -50259,10 +50259,10 @@
         <v>1.26</v>
       </c>
       <c r="X646" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y646" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="647" spans="1:25" x14ac:dyDescent="0.2">
@@ -50336,10 +50336,10 @@
         <v>1.26</v>
       </c>
       <c r="X647" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y647" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="648" spans="1:25" x14ac:dyDescent="0.2">
@@ -50413,10 +50413,10 @@
         <v>1.26</v>
       </c>
       <c r="X648" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y648" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="649" spans="1:25" x14ac:dyDescent="0.2">
@@ -50490,10 +50490,10 @@
         <v>1.26</v>
       </c>
       <c r="X649" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y649" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="650" spans="1:25" x14ac:dyDescent="0.2">
@@ -50567,10 +50567,10 @@
         <v>1.26</v>
       </c>
       <c r="X650" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y650" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="651" spans="1:25" x14ac:dyDescent="0.2">
@@ -50644,10 +50644,10 @@
         <v>1.26</v>
       </c>
       <c r="X651" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y651" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="652" spans="1:25" x14ac:dyDescent="0.2">
@@ -50721,10 +50721,10 @@
         <v>1.26</v>
       </c>
       <c r="X652" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y652" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="653" spans="1:25" x14ac:dyDescent="0.2">
@@ -50798,10 +50798,10 @@
         <v>1.26</v>
       </c>
       <c r="X653" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y653" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="654" spans="1:25" x14ac:dyDescent="0.2">
@@ -50875,10 +50875,10 @@
         <v>1.26</v>
       </c>
       <c r="X654" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y654" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="655" spans="1:25" x14ac:dyDescent="0.2">
@@ -50952,10 +50952,10 @@
         <v>1.26</v>
       </c>
       <c r="X655" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y655" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="656" spans="1:25" x14ac:dyDescent="0.2">
@@ -51029,10 +51029,10 @@
         <v>1.26</v>
       </c>
       <c r="X656" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y656" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="657" spans="1:25" x14ac:dyDescent="0.2">
@@ -51106,10 +51106,10 @@
         <v>1.26</v>
       </c>
       <c r="X657" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y657" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="658" spans="1:25" x14ac:dyDescent="0.2">
@@ -51183,10 +51183,10 @@
         <v>1.26</v>
       </c>
       <c r="X658" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y658" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="659" spans="1:25" x14ac:dyDescent="0.2">
@@ -51260,10 +51260,10 @@
         <v>1.26</v>
       </c>
       <c r="X659" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y659" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="660" spans="1:25" x14ac:dyDescent="0.2">
@@ -51337,10 +51337,10 @@
         <v>1.26</v>
       </c>
       <c r="X660" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y660" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="661" spans="1:25" x14ac:dyDescent="0.2">
@@ -51414,10 +51414,10 @@
         <v>1.26</v>
       </c>
       <c r="X661" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y661" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="662" spans="1:25" x14ac:dyDescent="0.2">
@@ -51491,10 +51491,10 @@
         <v>1.26</v>
       </c>
       <c r="X662" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y662" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="663" spans="1:25" x14ac:dyDescent="0.2">
@@ -51568,10 +51568,10 @@
         <v>1.26</v>
       </c>
       <c r="X663" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y663" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="664" spans="1:25" x14ac:dyDescent="0.2">
@@ -51645,10 +51645,10 @@
         <v>1.26</v>
       </c>
       <c r="X664" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y664" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="665" spans="1:25" x14ac:dyDescent="0.2">
@@ -51722,10 +51722,10 @@
         <v>1.26</v>
       </c>
       <c r="X665" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y665" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="666" spans="1:25" x14ac:dyDescent="0.2">
@@ -51799,10 +51799,10 @@
         <v>1.26</v>
       </c>
       <c r="X666" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y666" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="667" spans="1:25" x14ac:dyDescent="0.2">
@@ -51876,10 +51876,10 @@
         <v>1.26</v>
       </c>
       <c r="X667" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y667" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="668" spans="1:25" x14ac:dyDescent="0.2">
@@ -51953,10 +51953,10 @@
         <v>1.26</v>
       </c>
       <c r="X668" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y668" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="669" spans="1:25" x14ac:dyDescent="0.2">
@@ -52030,10 +52030,10 @@
         <v>1.26</v>
       </c>
       <c r="X669" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y669" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="670" spans="1:25" x14ac:dyDescent="0.2">
@@ -52107,10 +52107,10 @@
         <v>1.26</v>
       </c>
       <c r="X670" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y670" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="671" spans="1:25" x14ac:dyDescent="0.2">
@@ -52184,10 +52184,10 @@
         <v>1.26</v>
       </c>
       <c r="X671" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y671" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="672" spans="1:25" x14ac:dyDescent="0.2">
@@ -52261,10 +52261,10 @@
         <v>1.26</v>
       </c>
       <c r="X672" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y672" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="673" spans="1:25" x14ac:dyDescent="0.2">
@@ -52338,10 +52338,10 @@
         <v>1.26</v>
       </c>
       <c r="X673" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y673" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="674" spans="1:25" x14ac:dyDescent="0.2">
@@ -52415,10 +52415,10 @@
         <v>1.26</v>
       </c>
       <c r="X674" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y674" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="675" spans="1:25" x14ac:dyDescent="0.2">
@@ -52492,10 +52492,10 @@
         <v>1.26</v>
       </c>
       <c r="X675" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y675" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="676" spans="1:25" x14ac:dyDescent="0.2">
@@ -52569,10 +52569,10 @@
         <v>1.26</v>
       </c>
       <c r="X676" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y676" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="677" spans="1:25" x14ac:dyDescent="0.2">
@@ -52646,10 +52646,10 @@
         <v>1.26</v>
       </c>
       <c r="X677" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y677" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="678" spans="1:25" x14ac:dyDescent="0.2">
@@ -52723,10 +52723,10 @@
         <v>1.26</v>
       </c>
       <c r="X678" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y678" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="679" spans="1:25" x14ac:dyDescent="0.2">
@@ -52800,10 +52800,10 @@
         <v>1.26</v>
       </c>
       <c r="X679" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y679" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="680" spans="1:25" x14ac:dyDescent="0.2">
@@ -52877,10 +52877,10 @@
         <v>1.26</v>
       </c>
       <c r="X680" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y680" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="681" spans="1:25" x14ac:dyDescent="0.2">
@@ -52954,10 +52954,10 @@
         <v>1.26</v>
       </c>
       <c r="X681" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y681" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="682" spans="1:25" x14ac:dyDescent="0.2">
@@ -53031,10 +53031,10 @@
         <v>1.26</v>
       </c>
       <c r="X682" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y682" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="683" spans="1:25" x14ac:dyDescent="0.2">
@@ -53108,10 +53108,10 @@
         <v>1.26</v>
       </c>
       <c r="X683" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y683" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="684" spans="1:25" x14ac:dyDescent="0.2">
@@ -53185,10 +53185,10 @@
         <v>1.26</v>
       </c>
       <c r="X684" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y684" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="685" spans="1:25" x14ac:dyDescent="0.2">
@@ -53262,10 +53262,10 @@
         <v>1.26</v>
       </c>
       <c r="X685" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y685" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="686" spans="1:25" x14ac:dyDescent="0.2">
@@ -53339,10 +53339,10 @@
         <v>1.26</v>
       </c>
       <c r="X686" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y686" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="687" spans="1:25" x14ac:dyDescent="0.2">
@@ -53416,10 +53416,10 @@
         <v>1.26</v>
       </c>
       <c r="X687" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y687" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="688" spans="1:25" x14ac:dyDescent="0.2">
@@ -53493,10 +53493,10 @@
         <v>1.26</v>
       </c>
       <c r="X688" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y688" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="689" spans="1:25" x14ac:dyDescent="0.2">
@@ -53570,10 +53570,10 @@
         <v>1.26</v>
       </c>
       <c r="X689" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y689" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="690" spans="1:25" x14ac:dyDescent="0.2">
@@ -53647,10 +53647,10 @@
         <v>1.26</v>
       </c>
       <c r="X690" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y690" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="691" spans="1:25" x14ac:dyDescent="0.2">
@@ -53724,10 +53724,10 @@
         <v>1.26</v>
       </c>
       <c r="X691" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y691" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="692" spans="1:25" x14ac:dyDescent="0.2">
@@ -53801,10 +53801,10 @@
         <v>1.26</v>
       </c>
       <c r="X692" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y692" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="693" spans="1:25" x14ac:dyDescent="0.2">
@@ -53878,10 +53878,10 @@
         <v>1.26</v>
       </c>
       <c r="X693" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y693" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="694" spans="1:25" x14ac:dyDescent="0.2">
@@ -53955,10 +53955,10 @@
         <v>1.26</v>
       </c>
       <c r="X694" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y694" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="695" spans="1:25" x14ac:dyDescent="0.2">
@@ -54032,10 +54032,10 @@
         <v>1.26</v>
       </c>
       <c r="X695" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y695" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="696" spans="1:25" x14ac:dyDescent="0.2">
@@ -54109,10 +54109,10 @@
         <v>1.26</v>
       </c>
       <c r="X696" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y696" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="697" spans="1:25" x14ac:dyDescent="0.2">
@@ -54186,10 +54186,10 @@
         <v>1.26</v>
       </c>
       <c r="X697" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y697" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="698" spans="1:25" x14ac:dyDescent="0.2">
@@ -54263,10 +54263,10 @@
         <v>1.26</v>
       </c>
       <c r="X698" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y698" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="699" spans="1:25" x14ac:dyDescent="0.2">
@@ -54340,10 +54340,10 @@
         <v>1.26</v>
       </c>
       <c r="X699" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y699" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="700" spans="1:25" x14ac:dyDescent="0.2">
@@ -54417,10 +54417,10 @@
         <v>1.26</v>
       </c>
       <c r="X700" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y700" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
